--- a/output/spreadsheet/pyg_sl_2026.xlsx
+++ b/output/spreadsheet/pyg_sl_2026.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q109"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -852,7 +852,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 04/04/2026 12:00 h</t>
+          <t>Actualizado: 10/04/2026 11:47 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -4657,51 +4657,51 @@
       <c r="B61" s="34" t="n"/>
       <c r="C61" s="34" t="n"/>
       <c r="D61" s="35">
-        <f>D5-D33</f>
+        <f>D5-D34-D41-D50-D54</f>
         <v/>
       </c>
       <c r="E61" s="35">
-        <f>E5-E33</f>
+        <f>E5-E34-E41-E50-E54</f>
         <v/>
       </c>
       <c r="F61" s="35">
-        <f>F5-F33</f>
+        <f>F5-F34-F41-F50-F54</f>
         <v/>
       </c>
       <c r="G61" s="35">
-        <f>G5-G33</f>
+        <f>G5-G34-G41-G50-G54</f>
         <v/>
       </c>
       <c r="H61" s="35">
-        <f>H5-H33</f>
+        <f>H5-H34-H41-H50-H54</f>
         <v/>
       </c>
       <c r="I61" s="35">
-        <f>I5-I33</f>
+        <f>I5-I34-I41-I50-I54</f>
         <v/>
       </c>
       <c r="J61" s="35">
-        <f>J5-J33</f>
+        <f>J5-J34-J41-J50-J54</f>
         <v/>
       </c>
       <c r="K61" s="35">
-        <f>K5-K33</f>
+        <f>K5-K34-K41-K50-K54</f>
         <v/>
       </c>
       <c r="L61" s="35">
-        <f>L5-L33</f>
+        <f>L5-L34-L41-L50-L54</f>
         <v/>
       </c>
       <c r="M61" s="35">
-        <f>M5-M33</f>
+        <f>M5-M34-M41-M50-M54</f>
         <v/>
       </c>
       <c r="N61" s="35">
-        <f>N5-N33</f>
+        <f>N5-N34-N41-N50-N54</f>
         <v/>
       </c>
       <c r="O61" s="35">
-        <f>O5-O33</f>
+        <f>O5-O34-O41-O50-O54</f>
         <v/>
       </c>
       <c r="P61" s="9">
@@ -4807,51 +4807,51 @@
       </c>
       <c r="C64" s="13" t="n"/>
       <c r="D64" s="14">
-        <f>D65+D75+D78+D89+D105</f>
+        <f>D65+D75+D78+D90+D107</f>
         <v/>
       </c>
       <c r="E64" s="14">
-        <f>E65+E75+E78+E89+E105</f>
+        <f>E65+E75+E78+E90+E107</f>
         <v/>
       </c>
       <c r="F64" s="14">
-        <f>F65+F75+F78+F89+F105</f>
+        <f>F65+F75+F78+F90+F107</f>
         <v/>
       </c>
       <c r="G64" s="14">
-        <f>G65+G75+G78+G89+G105</f>
+        <f>G65+G75+G78+G90+G107</f>
         <v/>
       </c>
       <c r="H64" s="14">
-        <f>H65+H75+H78+H89+H105</f>
+        <f>H65+H75+H78+H90+H107</f>
         <v/>
       </c>
       <c r="I64" s="14">
-        <f>I65+I75+I78+I89+I105</f>
+        <f>I65+I75+I78+I90+I107</f>
         <v/>
       </c>
       <c r="J64" s="14">
-        <f>J65+J75+J78+J89+J105</f>
+        <f>J65+J75+J78+J90+J107</f>
         <v/>
       </c>
       <c r="K64" s="14">
-        <f>K65+K75+K78+K89+K105</f>
+        <f>K65+K75+K78+K90+K107</f>
         <v/>
       </c>
       <c r="L64" s="14">
-        <f>L65+L75+L78+L89+L105</f>
+        <f>L65+L75+L78+L90+L107</f>
         <v/>
       </c>
       <c r="M64" s="14">
-        <f>M65+M75+M78+M89+M105</f>
+        <f>M65+M75+M78+M90+M107</f>
         <v/>
       </c>
       <c r="N64" s="14">
-        <f>N65+N75+N78+N89+N105</f>
+        <f>N65+N75+N78+N90+N107</f>
         <v/>
       </c>
       <c r="O64" s="14">
-        <f>O65+O75+O78+O89+O105</f>
+        <f>O65+O75+O78+O90+O107</f>
         <v/>
       </c>
       <c r="P64" s="15">
@@ -5779,51 +5779,51 @@
         </is>
       </c>
       <c r="D78" s="20">
-        <f>D79+D80+D81+D85+D86+D87+D88</f>
+        <f>D79+D80+D81+D82+D86+D87+D88+D89</f>
         <v/>
       </c>
       <c r="E78" s="20">
-        <f>E79+E80+E81+E85+E86+E87+E88</f>
+        <f>E79+E80+E81+E82+E86+E87+E88+E89</f>
         <v/>
       </c>
       <c r="F78" s="20">
-        <f>F79+F80+F81+F85+F86+F87+F88</f>
+        <f>F79+F80+F81+F82+F86+F87+F88+F89</f>
         <v/>
       </c>
       <c r="G78" s="20">
-        <f>G79+G80+G81+G85+G86+G87+G88</f>
+        <f>G79+G80+G81+G82+G86+G87+G88+G89</f>
         <v/>
       </c>
       <c r="H78" s="20">
-        <f>H79+H80+H81+H85+H86+H87+H88</f>
+        <f>H79+H80+H81+H82+H86+H87+H88+H89</f>
         <v/>
       </c>
       <c r="I78" s="20">
-        <f>I79+I80+I81+I85+I86+I87+I88</f>
+        <f>I79+I80+I81+I82+I86+I87+I88+I89</f>
         <v/>
       </c>
       <c r="J78" s="20">
-        <f>J79+J80+J81+J85+J86+J87+J88</f>
+        <f>J79+J80+J81+J82+J86+J87+J88+J89</f>
         <v/>
       </c>
       <c r="K78" s="20">
-        <f>K79+K80+K81+K85+K86+K87+K88</f>
+        <f>K79+K80+K81+K82+K86+K87+K88+K89</f>
         <v/>
       </c>
       <c r="L78" s="20">
-        <f>L79+L80+L81+L85+L86+L87+L88</f>
+        <f>L79+L80+L81+L82+L86+L87+L88+L89</f>
         <v/>
       </c>
       <c r="M78" s="20">
-        <f>M79+M80+M81+M85+M86+M87+M88</f>
+        <f>M79+M80+M81+M82+M86+M87+M88+M89</f>
         <v/>
       </c>
       <c r="N78" s="20">
-        <f>N79+N80+N81+N85+N86+N87+N88</f>
+        <f>N79+N80+N81+N82+N86+N87+N88+N89</f>
         <v/>
       </c>
       <c r="O78" s="20">
-        <f>O79+O80+O81+O85+O86+O87+O88</f>
+        <f>O79+O80+O81+O82+O86+O87+O88+O89</f>
         <v/>
       </c>
       <c r="P78" s="21">
@@ -5979,13 +5979,13 @@
     <row r="81" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            HANNUN</t>
+          <t xml:space="preserve">            CONTASIMPLE</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="D81" s="5">
@@ -6049,61 +6049,61 @@
     <row r="82" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            administration</t>
+          <t xml:space="preserve">            HANNUN</t>
         </is>
       </c>
       <c r="B82" s="4" t="n"/>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="E82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="F82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="G82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="H82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="I82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="J82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="K82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="L82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="M82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="N82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="O82" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C82)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82)</f>
         <v/>
       </c>
       <c r="P82" s="24">
@@ -6119,61 +6119,61 @@
     <row r="83" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            office</t>
+          <t xml:space="preserve">            administration</t>
         </is>
       </c>
       <c r="B83" s="4" t="n"/>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="E83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="F83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="G83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="H83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="I83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="J83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="K83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="L83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="M83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="N83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="O83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
         <v/>
       </c>
       <c r="P83" s="24">
@@ -6186,64 +6186,64 @@
         </is>
       </c>
     </row>
-    <row r="84" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="84" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            services</t>
+          <t xml:space="preserve">            office</t>
         </is>
       </c>
       <c r="B84" s="4" t="n"/>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="E84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="F84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="G84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="H84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="I84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="J84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="K84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="L84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="M84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="N84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="O84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C81,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="P84" s="24">
@@ -6256,64 +6256,64 @@
         </is>
       </c>
     </row>
-    <row r="85" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="85" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            NODA</t>
+          <t xml:space="preserve">            services</t>
         </is>
       </c>
       <c r="B85" s="4" t="n"/>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>services</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="E85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="F85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="G85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="H85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="I85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="J85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="K85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="L85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="M85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="N85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="O85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="P85" s="24">
@@ -6329,13 +6329,13 @@
     <row r="86" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            REGUS</t>
+          <t xml:space="preserve">            NODA</t>
         </is>
       </c>
       <c r="B86" s="4" t="n"/>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="D86" s="5">
@@ -6399,13 +6399,13 @@
     <row r="87" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            TORRAS</t>
+          <t xml:space="preserve">            REGUS</t>
         </is>
       </c>
       <c r="B87" s="4" t="n"/>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="D87" s="5">
@@ -6466,16 +6466,16 @@
         </is>
       </c>
     </row>
-    <row r="88" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="88" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            VITALY</t>
+          <t xml:space="preserve">            TORRAS</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="D88" s="5">
@@ -6536,141 +6536,141 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="12" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
+    <row r="89" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            VITALY</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>VITALY</t>
+        </is>
+      </c>
+      <c r="D89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="E89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="F89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="G89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="H89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="I89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="J89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="K89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="L89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="M89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="N89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="O89" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C89)</f>
+        <v/>
+      </c>
+      <c r="P89" s="24">
+        <f>SUM(D89:O89)</f>
+        <v/>
+      </c>
+      <c r="Q89" s="25" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="12" customHeight="1">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">        Technology</t>
         </is>
       </c>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="19" t="inlineStr">
+      <c r="B90" s="18" t="n"/>
+      <c r="C90" s="19" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D89" s="20">
-        <f>SUM(D90:D104)</f>
-        <v/>
-      </c>
-      <c r="E89" s="20">
-        <f>SUM(E90:E104)</f>
-        <v/>
-      </c>
-      <c r="F89" s="20">
-        <f>SUM(F90:F104)</f>
-        <v/>
-      </c>
-      <c r="G89" s="20">
-        <f>SUM(G90:G104)</f>
-        <v/>
-      </c>
-      <c r="H89" s="20">
-        <f>SUM(H90:H104)</f>
-        <v/>
-      </c>
-      <c r="I89" s="20">
-        <f>SUM(I90:I104)</f>
-        <v/>
-      </c>
-      <c r="J89" s="20">
-        <f>SUM(J90:J104)</f>
-        <v/>
-      </c>
-      <c r="K89" s="20">
-        <f>SUM(K90:K104)</f>
-        <v/>
-      </c>
-      <c r="L89" s="20">
-        <f>SUM(L90:L104)</f>
-        <v/>
-      </c>
-      <c r="M89" s="20">
-        <f>SUM(M90:M104)</f>
-        <v/>
-      </c>
-      <c r="N89" s="20">
-        <f>SUM(N90:N104)</f>
-        <v/>
-      </c>
-      <c r="O89" s="20">
-        <f>SUM(O90:O104)</f>
-        <v/>
-      </c>
-      <c r="P89" s="21">
-        <f>SUM(D89:O89)</f>
-        <v/>
-      </c>
-      <c r="Q89" s="22" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A90" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            ADOBE</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>ADOBE</t>
-        </is>
-      </c>
-      <c r="D90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="E90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="F90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="G90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="H90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="I90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="J90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="K90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="L90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="M90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="N90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="O90" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C90)</f>
-        <v/>
-      </c>
-      <c r="P90" s="24">
+      <c r="D90" s="20">
+        <f>SUM(D91:D106)</f>
+        <v/>
+      </c>
+      <c r="E90" s="20">
+        <f>SUM(E91:E106)</f>
+        <v/>
+      </c>
+      <c r="F90" s="20">
+        <f>SUM(F91:F106)</f>
+        <v/>
+      </c>
+      <c r="G90" s="20">
+        <f>SUM(G91:G106)</f>
+        <v/>
+      </c>
+      <c r="H90" s="20">
+        <f>SUM(H91:H106)</f>
+        <v/>
+      </c>
+      <c r="I90" s="20">
+        <f>SUM(I91:I106)</f>
+        <v/>
+      </c>
+      <c r="J90" s="20">
+        <f>SUM(J91:J106)</f>
+        <v/>
+      </c>
+      <c r="K90" s="20">
+        <f>SUM(K91:K106)</f>
+        <v/>
+      </c>
+      <c r="L90" s="20">
+        <f>SUM(L91:L106)</f>
+        <v/>
+      </c>
+      <c r="M90" s="20">
+        <f>SUM(M91:M106)</f>
+        <v/>
+      </c>
+      <c r="N90" s="20">
+        <f>SUM(N91:N106)</f>
+        <v/>
+      </c>
+      <c r="O90" s="20">
+        <f>SUM(O91:O106)</f>
+        <v/>
+      </c>
+      <c r="P90" s="21">
         <f>SUM(D90:O90)</f>
         <v/>
       </c>
-      <c r="Q90" s="25" t="inlineStr">
+      <c r="Q90" s="22" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -6679,13 +6679,13 @@
     <row r="91" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            CANVA</t>
+          <t xml:space="preserve">            ADOBE</t>
         </is>
       </c>
       <c r="B91" s="4" t="n"/>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D91" s="5">
@@ -6749,13 +6749,13 @@
     <row r="92" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GODADDY</t>
+          <t xml:space="preserve">            CANVA</t>
         </is>
       </c>
       <c r="B92" s="4" t="n"/>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="D92" s="5">
@@ -6819,13 +6819,13 @@
     <row r="93" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GOOGLEWORKSPACE</t>
+          <t xml:space="preserve">            GODADDY</t>
         </is>
       </c>
       <c r="B93" s="4" t="n"/>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="D93" s="5">
@@ -6889,13 +6889,13 @@
     <row r="94" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A94" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GORGIAS</t>
+          <t xml:space="preserve">            GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="B94" s="4" t="n"/>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="D94" s="5">
@@ -6959,13 +6959,13 @@
     <row r="95" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            HETZNER</t>
+          <t xml:space="preserve">            GORGIAS</t>
         </is>
       </c>
       <c r="B95" s="4" t="n"/>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="D95" s="5">
@@ -7029,13 +7029,13 @@
     <row r="96" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            KONVOAI</t>
+          <t xml:space="preserve">            HETZNER</t>
         </is>
       </c>
       <c r="B96" s="4" t="n"/>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D96" s="5">
@@ -7099,13 +7099,13 @@
     <row r="97" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            MASMOVIL</t>
+          <t xml:space="preserve">            KONVOAI</t>
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="D97" s="5">
@@ -7169,13 +7169,13 @@
     <row r="98" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            MICROSOFT</t>
+          <t xml:space="preserve">            MASMOVIL</t>
         </is>
       </c>
       <c r="B98" s="4" t="n"/>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="D98" s="5">
@@ -7239,13 +7239,13 @@
     <row r="99" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            OPENAI</t>
+          <t xml:space="preserve">            MICROSOFT</t>
         </is>
       </c>
       <c r="B99" s="4" t="n"/>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D99" s="5">
@@ -7309,13 +7309,13 @@
     <row r="100" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A100" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            PRODUCTHERO</t>
+          <t xml:space="preserve">            OPENAI</t>
         </is>
       </c>
       <c r="B100" s="4" t="n"/>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="D100" s="5">
@@ -7379,13 +7379,13 @@
     <row r="101" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            RAILWAY</t>
+          <t xml:space="preserve">            PRODUCTHERO</t>
         </is>
       </c>
       <c r="B101" s="4" t="n"/>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="D101" s="5">
@@ -7449,13 +7449,13 @@
     <row r="102" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A102" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            REVER</t>
+          <t xml:space="preserve">            RAILWAY</t>
         </is>
       </c>
       <c r="B102" s="4" t="n"/>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D102" s="5">
@@ -7519,13 +7519,13 @@
     <row r="103" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            SHOPIFY</t>
+          <t xml:space="preserve">            REVER</t>
         </is>
       </c>
       <c r="B103" s="4" t="n"/>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -7586,16 +7586,16 @@
         </is>
       </c>
     </row>
-    <row r="104" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="104" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A104" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            YUMAAI</t>
+          <t xml:space="preserve">            SHOPIFY</t>
         </is>
       </c>
       <c r="B104" s="4" t="n"/>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="D104" s="5">
@@ -7656,255 +7656,395 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="12" customHeight="1">
-      <c r="A105" s="17" t="inlineStr">
+    <row r="105" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A105" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            SYNCWITH</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>SYNCWITH</t>
+        </is>
+      </c>
+      <c r="D105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="E105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="F105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="G105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="H105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="I105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="J105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="K105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="L105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="M105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="N105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="O105" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C105)</f>
+        <v/>
+      </c>
+      <c r="P105" s="24">
+        <f>SUM(D105:O105)</f>
+        <v/>
+      </c>
+      <c r="Q105" s="25" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+      <c r="A106" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            YUMAAI</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="D106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="E106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="F106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="G106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="H106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="I106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="J106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="K106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="L106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="M106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="N106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="O106" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C106)</f>
+        <v/>
+      </c>
+      <c r="P106" s="24">
+        <f>SUM(D106:O106)</f>
+        <v/>
+      </c>
+      <c r="Q106" s="25" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="12" customHeight="1">
+      <c r="A107" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">        Uncategorized Expenses</t>
         </is>
       </c>
-      <c r="B105" s="18" t="n"/>
-      <c r="C105" s="19" t="inlineStr">
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="19" t="inlineStr">
         <is>
           <t>Uncategorized Expenses</t>
         </is>
       </c>
-      <c r="D105" s="20">
+      <c r="D107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="E105" s="20">
+      <c r="E107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="F105" s="20">
+      <c r="F107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="G105" s="20">
+      <c r="G107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="H105" s="20">
+      <c r="H107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="I105" s="20">
+      <c r="I107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="J105" s="20">
+      <c r="J107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="K105" s="20">
+      <c r="K107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="L105" s="20">
+      <c r="L107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="M105" s="20">
+      <c r="M107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="N105" s="20">
+      <c r="N107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="O105" s="20">
+      <c r="O107" s="20">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
         <v/>
       </c>
-      <c r="P105" s="21">
-        <f>SUM(D105:O105)</f>
-        <v/>
-      </c>
-      <c r="Q105" s="22" t="inlineStr">
+      <c r="P107" s="21">
+        <f>SUM(D107:O107)</f>
+        <v/>
+      </c>
+      <c r="Q107" s="22" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="12" customHeight="1">
-      <c r="A106" s="17" t="inlineStr">
+    <row r="108" ht="12" customHeight="1">
+      <c r="A108" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">        Currency Adjustment</t>
         </is>
       </c>
-      <c r="B106" s="19" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>Currency Adjustment</t>
         </is>
       </c>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="20" t="n">
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="20" t="n">
         <v>-132.9</v>
       </c>
-      <c r="E106" s="20" t="n">
+      <c r="E108" s="20" t="n">
         <v>-277.52</v>
       </c>
-      <c r="F106" s="20" t="n"/>
-      <c r="G106" s="20" t="n"/>
-      <c r="H106" s="20" t="n"/>
-      <c r="I106" s="20" t="n"/>
-      <c r="J106" s="20" t="n"/>
-      <c r="K106" s="20" t="n"/>
-      <c r="L106" s="20" t="n"/>
-      <c r="M106" s="20" t="n"/>
-      <c r="N106" s="20" t="n"/>
-      <c r="O106" s="20" t="n"/>
-      <c r="P106" s="21">
-        <f>SUM(D106:O106)</f>
-        <v/>
-      </c>
-      <c r="Q106" s="27" t="n"/>
-    </row>
-    <row r="107" ht="12" customHeight="1">
-      <c r="A107" s="4" t="n"/>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="5" t="n"/>
-      <c r="F107" s="5" t="n"/>
-      <c r="G107" s="5" t="n"/>
-      <c r="H107" s="5" t="n"/>
-      <c r="I107" s="5" t="n"/>
-      <c r="J107" s="5" t="n"/>
-      <c r="K107" s="5" t="n"/>
-      <c r="L107" s="5" t="n"/>
-      <c r="M107" s="5" t="n"/>
-      <c r="N107" s="5" t="n"/>
-      <c r="O107" s="5" t="n"/>
-      <c r="P107" s="24">
-        <f>SUM(D107:O107)</f>
-        <v/>
-      </c>
-      <c r="Q107" s="5" t="n"/>
-    </row>
-    <row r="108" ht="12" customHeight="1">
-      <c r="A108" s="33" t="inlineStr">
+      <c r="F108" s="20" t="n"/>
+      <c r="G108" s="20" t="n"/>
+      <c r="H108" s="20" t="n"/>
+      <c r="I108" s="20" t="n"/>
+      <c r="J108" s="20" t="n"/>
+      <c r="K108" s="20" t="n"/>
+      <c r="L108" s="20" t="n"/>
+      <c r="M108" s="20" t="n"/>
+      <c r="N108" s="20" t="n"/>
+      <c r="O108" s="20" t="n"/>
+      <c r="P108" s="21">
+        <f>SUM(D108:O108)</f>
+        <v/>
+      </c>
+      <c r="Q108" s="27" t="n"/>
+    </row>
+    <row r="109" ht="12" customHeight="1">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="5" t="n"/>
+      <c r="F109" s="5" t="n"/>
+      <c r="G109" s="5" t="n"/>
+      <c r="H109" s="5" t="n"/>
+      <c r="I109" s="5" t="n"/>
+      <c r="J109" s="5" t="n"/>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="5" t="n"/>
+      <c r="M109" s="5" t="n"/>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="24">
+        <f>SUM(D109:O109)</f>
+        <v/>
+      </c>
+      <c r="Q109" s="5" t="n"/>
+    </row>
+    <row r="110" ht="12" customHeight="1">
+      <c r="A110" s="33" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B108" s="34" t="n"/>
-      <c r="C108" s="34" t="n"/>
-      <c r="D108" s="35">
-        <f>D4-D33-D64-D106</f>
-        <v/>
-      </c>
-      <c r="E108" s="35">
-        <f>E4-E33-E64-E106</f>
-        <v/>
-      </c>
-      <c r="F108" s="35">
-        <f>F4-F33-F64-F106</f>
-        <v/>
-      </c>
-      <c r="G108" s="35">
-        <f>G4-G33-G64-G106</f>
-        <v/>
-      </c>
-      <c r="H108" s="35">
-        <f>H4-H33-H64-H106</f>
-        <v/>
-      </c>
-      <c r="I108" s="35">
-        <f>I4-I33-I64-I106</f>
-        <v/>
-      </c>
-      <c r="J108" s="35">
-        <f>J4-J33-J64-J106</f>
-        <v/>
-      </c>
-      <c r="K108" s="35">
-        <f>K4-K33-K64-K106</f>
-        <v/>
-      </c>
-      <c r="L108" s="35">
-        <f>L4-L33-L64-L106</f>
-        <v/>
-      </c>
-      <c r="M108" s="35">
-        <f>M4-M33-M64-M106</f>
-        <v/>
-      </c>
-      <c r="N108" s="35">
-        <f>N4-N33-N64-N106</f>
-        <v/>
-      </c>
-      <c r="O108" s="35">
-        <f>O4-O33-O64-O106</f>
-        <v/>
-      </c>
-      <c r="P108" s="9">
-        <f>SUM(D108:O108)</f>
-        <v/>
-      </c>
-      <c r="Q108" s="36" t="n"/>
-    </row>
-    <row r="109" ht="12" customHeight="1">
-      <c r="A109" s="37" t="inlineStr">
+      <c r="B110" s="34" t="n"/>
+      <c r="C110" s="34" t="n"/>
+      <c r="D110" s="35">
+        <f>D4-D33-D64-D108</f>
+        <v/>
+      </c>
+      <c r="E110" s="35">
+        <f>E4-E33-E64-E108</f>
+        <v/>
+      </c>
+      <c r="F110" s="35">
+        <f>F4-F33-F64-F108</f>
+        <v/>
+      </c>
+      <c r="G110" s="35">
+        <f>G4-G33-G64-G108</f>
+        <v/>
+      </c>
+      <c r="H110" s="35">
+        <f>H4-H33-H64-H108</f>
+        <v/>
+      </c>
+      <c r="I110" s="35">
+        <f>I4-I33-I64-I108</f>
+        <v/>
+      </c>
+      <c r="J110" s="35">
+        <f>J4-J33-J64-J108</f>
+        <v/>
+      </c>
+      <c r="K110" s="35">
+        <f>K4-K33-K64-K108</f>
+        <v/>
+      </c>
+      <c r="L110" s="35">
+        <f>L4-L33-L64-L108</f>
+        <v/>
+      </c>
+      <c r="M110" s="35">
+        <f>M4-M33-M64-M108</f>
+        <v/>
+      </c>
+      <c r="N110" s="35">
+        <f>N4-N33-N64-N108</f>
+        <v/>
+      </c>
+      <c r="O110" s="35">
+        <f>O4-O33-O64-O108</f>
+        <v/>
+      </c>
+      <c r="P110" s="9">
+        <f>SUM(D110:O110)</f>
+        <v/>
+      </c>
+      <c r="Q110" s="36" t="n"/>
+    </row>
+    <row r="111" ht="12" customHeight="1">
+      <c r="A111" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">        % profit / product sales</t>
         </is>
       </c>
-      <c r="B109" s="38" t="n"/>
-      <c r="C109" s="38" t="n"/>
-      <c r="D109" s="39">
-        <f>IFERROR(D108/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E109" s="39">
-        <f>IFERROR(E108/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F109" s="39">
-        <f>IFERROR(F108/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G109" s="39">
-        <f>IFERROR(G108/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H109" s="39">
-        <f>IFERROR(H108/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I109" s="39">
-        <f>IFERROR(I108/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J109" s="39">
-        <f>IFERROR(J108/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K109" s="39">
-        <f>IFERROR(K108/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L109" s="39">
-        <f>IFERROR(L108/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M109" s="39">
-        <f>IFERROR(M108/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N109" s="39">
-        <f>IFERROR(N108/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O109" s="39">
-        <f>IFERROR(O108/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P109" s="40">
-        <f>IFERROR(P108/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q109" s="31" t="n"/>
+      <c r="B111" s="38" t="n"/>
+      <c r="C111" s="38" t="n"/>
+      <c r="D111" s="39">
+        <f>IFERROR(D110/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E111" s="39">
+        <f>IFERROR(E110/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F111" s="39">
+        <f>IFERROR(F110/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G111" s="39">
+        <f>IFERROR(G110/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H111" s="39">
+        <f>IFERROR(H110/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I111" s="39">
+        <f>IFERROR(I110/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J111" s="39">
+        <f>IFERROR(J110/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K111" s="39">
+        <f>IFERROR(K110/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L111" s="39">
+        <f>IFERROR(L110/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M111" s="39">
+        <f>IFERROR(M110/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N111" s="39">
+        <f>IFERROR(N110/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O111" s="39">
+        <f>IFERROR(O110/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P111" s="40">
+        <f>IFERROR(P110/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q111" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7992,6 +8132,8 @@
     <hyperlink ref="Q103" location="'g-expenses-sl'!A1" display="-&gt;"/>
     <hyperlink ref="Q104" location="'g-expenses-sl'!A1" display="-&gt;"/>
     <hyperlink ref="Q105" location="'g-expenses-sl'!A1" display="-&gt;"/>
+    <hyperlink ref="Q106" location="'g-expenses-sl'!A1" display="-&gt;"/>
+    <hyperlink ref="Q107" location="'g-expenses-sl'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8003,7 +8145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8105,7 +8247,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -8114,10 +8256,10 @@
         </is>
       </c>
       <c r="E4" s="48" t="n">
-        <v>1.1919</v>
+        <v>0.8662</v>
       </c>
       <c r="F4" s="48" t="n">
-        <v>0.83899656</v>
+        <v>1.15446779</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -8128,17 +8270,17 @@
     <row r="5" ht="12" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8147,14 +8289,14 @@
         </is>
       </c>
       <c r="E5" s="48" t="n">
-        <v>1</v>
+        <v>1.1919</v>
       </c>
       <c r="F5" s="48" t="n">
-        <v>1</v>
+        <v>0.83899656</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
@@ -8166,12 +8308,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8180,31 +8322,31 @@
         </is>
       </c>
       <c r="E6" s="48" t="n">
-        <v>1.1805</v>
+        <v>1</v>
       </c>
       <c r="F6" s="48" t="n">
-        <v>0.84709869</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
+          <t>identity</t>
         </is>
       </c>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8213,26 +8355,26 @@
         </is>
       </c>
       <c r="E7" s="48" t="n">
-        <v>1</v>
+        <v>0.8763</v>
       </c>
       <c r="F7" s="48" t="n">
-        <v>1</v>
+        <v>1.1411617</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8246,10 +8388,10 @@
         </is>
       </c>
       <c r="E8" s="48" t="n">
-        <v>1.1498</v>
+        <v>1.1805</v>
       </c>
       <c r="F8" s="48" t="n">
-        <v>0.86971647</v>
+        <v>0.84709869</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -8260,12 +8402,12 @@
     <row r="9" ht="12" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8293,33 +8435,693 @@
     <row r="10" ht="12" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="n">
+        <v>0.86833</v>
+      </c>
+      <c r="F10" s="48" t="n">
+        <v>1.1516359</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E11" s="48" t="n">
+        <v>1.1498</v>
+      </c>
+      <c r="F11" s="48" t="n">
+        <v>0.86971647</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>202604</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E13" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F13" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="12" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E10" s="48" t="n">
-        <v>1.1525</v>
-      </c>
-      <c r="F10" s="48" t="n">
-        <v>0.86767896</v>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F14" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F15" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202605)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="12" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F16" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202605)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="12" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F17" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202606)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="12" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F18" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202606)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E19" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F19" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202607)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="12" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E20" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F20" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202607)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="12" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E21" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F21" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202608)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="12" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F22" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202608)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E23" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F23" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F24" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E25" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F25" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E26" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F26" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="12" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>202611</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E27" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F27" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>202611</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E28" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F28" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="12" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E29" s="48" t="n">
+        <v>0.87053</v>
+      </c>
+      <c r="F29" s="48" t="n">
+        <v>1.14872549</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="12" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E30" s="48" t="n">
+        <v>1.1685</v>
+      </c>
+      <c r="F30" s="48" t="n">
+        <v>0.85579803</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
         </is>
       </c>
     </row>
@@ -8337,7 +9139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8711,17 +9513,17 @@
     <row r="16" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CEGID SMB, S.A.U</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>Contasimple</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8731,24 +9533,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bidirectional HANNUN relationship; incoming expense invoices and outgoing customer invoices</t>
+          <t>Accounting software subscription</t>
         </is>
       </c>
     </row>
     <row r="17" ht="12" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NODA Asesores</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8756,22 +9558,26 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Bidirectional HANNUN relationship; incoming expense invoices and outgoing customer invoices</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>regus</t>
+          <t>NODA Asesores</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -8784,17 +9590,17 @@
     <row r="19" ht="12" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>regus</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -8807,17 +9613,17 @@
     <row r="20" ht="12" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -8825,49 +9631,49 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Annual prevention and occupational health service</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21" ht="12" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>expenses/opex/marketing</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>expenses/opex/administration</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Annual prevention and occupational health service</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="12" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>METAADS</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>METAADS</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8880,67 +9686,67 @@
     <row r="23" ht="12" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOSCONSULTING</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DOSCONSULTING</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nóminas</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>expenses/opex/staff</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Monthly payroll management for SL</t>
-        </is>
-      </c>
+          <t>expenses/opex/marketing</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>DOSCONSULTING</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>DOSCONSULTING</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>Nóminas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>expenses/opex/technology</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>expenses/opex/staff</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Monthly payroll management for SL</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>canva</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8953,17 +9759,17 @@
     <row r="26" ht="12" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>godaddy</t>
+          <t>canva</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8976,17 +9782,17 @@
     <row r="27" ht="12" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>godaddy</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8999,17 +9805,17 @@
     <row r="28" ht="12" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gorgias</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -9022,17 +9828,17 @@
     <row r="29" ht="12" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>Gorgias</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -9045,17 +9851,17 @@
     <row r="30" ht="12" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>konvo</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9068,17 +9874,17 @@
     <row r="31" ht="12" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mas movil</t>
+          <t>konvo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -9091,17 +9897,17 @@
     <row r="32" ht="12" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>mas movil</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9114,17 +9920,17 @@
     <row r="33" ht="12" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9132,26 +9938,22 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Groups ChatGPT and API</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34" ht="12" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ProductHERO</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9159,22 +9961,26 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Groups ChatGPT and API</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="12" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>ProductHERO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -9187,17 +9993,17 @@
     <row r="36" ht="12" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -9210,17 +10016,17 @@
     <row r="37" ht="12" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -9233,17 +10039,17 @@
     <row r="38" ht="12" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YUMA</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -9256,106 +10062,156 @@
     <row r="39" ht="12" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LIVITUM</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LIVITUM</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>709. Rappels</t>
+          <t>SyncWith</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>income/other_income/rappels</t>
+          <t>expenses/opex/technology</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rappel issued to Livitum</t>
+          <t>Monthly subscription invoiced one month in arrears</t>
         </is>
       </c>
     </row>
     <row r="40" ht="12" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>YUMA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>income/sales/marketplaces</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Outgoing partner invoice</t>
-        </is>
-      </c>
+          <t>expenses/opex/technology</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41" ht="12" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>LIVITUM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>LIVITUM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>709. Rappels</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>income/sales/marketplaces</t>
+          <t>income/other_income/rappels</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Outgoing partner invoice</t>
+          <t>Rappel issued to Livitum</t>
         </is>
       </c>
     </row>
     <row r="42" ht="12" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
+          <t>CHOOSE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CHOOSE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CHOOSE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>income/sales/marketplaces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Outgoing partner invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="12" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>income/sales/marketplaces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Outgoing partner invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="12" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>income/shared-services</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Outgoing CNC rental invoice</t>
         </is>
@@ -9556,7 +10412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9733,13 +10589,13 @@
         <v>18</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" s="51" t="n">
         <v>0</v>
@@ -9766,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="51" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q4" s="51" t="n"/>
     </row>
@@ -9785,10 +10641,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" s="52" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" s="52" t="n">
         <v>0</v>
@@ -9815,7 +10671,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="52" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q5" s="52" t="n"/>
     </row>
@@ -9837,7 +10693,7 @@
         <v>9</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H6" s="54" t="n">
         <v>0</v>
@@ -9864,7 +10720,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="54" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="54" t="n"/>
     </row>
@@ -10113,8 +10969,8 @@
       <c r="F12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="56" t="n">
-        <v>0</v>
+      <c r="G12" t="n">
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10141,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1">
@@ -10251,8 +11107,8 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="56" t="n">
-        <v>0</v>
+      <c r="G15" t="n">
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10279,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
@@ -10297,7 +11153,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="54" t="n">
         <v>0</v>
@@ -10327,7 +11183,7 @@
         <v>0</v>
       </c>
       <c r="P16" s="54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q16" s="54" t="n"/>
     </row>
@@ -10344,9 +11200,9 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
@@ -10374,7 +11230,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
@@ -10672,10 +11528,10 @@
         <v>4</v>
       </c>
       <c r="E25" s="52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" s="52" t="n">
         <v>0</v>
@@ -10705,7 +11561,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q25" s="52" t="n"/>
     </row>
@@ -10722,9 +11578,9 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
@@ -10752,7 +11608,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1">
@@ -10765,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -10798,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="12" customHeight="1">
@@ -10814,9 +11670,9 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
@@ -10844,7 +11700,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="12" customHeight="1">
@@ -10860,9 +11716,9 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
@@ -10890,7 +11746,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" ht="12" customHeight="1">
@@ -10958,7 +11814,7 @@
         <v>47</v>
       </c>
       <c r="F32" s="51" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G32" s="51" t="n">
         <v>4</v>
@@ -10988,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="51" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="Q32" s="51" t="n"/>
     </row>
@@ -11007,7 +11863,7 @@
         <v>22</v>
       </c>
       <c r="F33" s="52" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G33" s="52" t="n">
         <v>2</v>
@@ -11037,7 +11893,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="52" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q33" s="52" t="n"/>
     </row>
@@ -11335,7 +12191,7 @@
         <v>7</v>
       </c>
       <c r="F40" s="54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G40" s="54" t="n">
         <v>0</v>
@@ -11365,7 +12221,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="54" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q40" s="54" t="n"/>
     </row>
@@ -11474,9 +12330,9 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
@@ -11504,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" ht="12" customHeight="1">
@@ -11990,7 +12846,7 @@
         <v>25</v>
       </c>
       <c r="F56" s="52" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G56" s="52" t="n">
         <v>2</v>
@@ -12020,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="52" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Q56" s="52" t="n"/>
     </row>
@@ -12603,7 +13459,7 @@
         <v>2</v>
       </c>
       <c r="F69" s="54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" s="54" t="n">
         <v>0</v>
@@ -12633,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q69" s="54" t="n"/>
     </row>
@@ -12698,8 +13554,8 @@
       <c r="F71" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="56" t="n">
-        <v>0</v>
+      <c r="G71" t="n">
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -12726,25 +13582,25 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1">
       <c r="C72" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
@@ -12772,25 +13628,25 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1">
       <c r="C73" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
@@ -12818,25 +13674,25 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1">
       <c r="C74" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
@@ -12864,13 +13720,13 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" ht="12" customHeight="1">
       <c r="C75" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -12880,9 +13736,9 @@
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
@@ -12910,25 +13766,25 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1">
       <c r="C76" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>services</t>
         </is>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
@@ -12956,17 +13812,17 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" ht="12" customHeight="1">
       <c r="C77" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -13002,25 +13858,25 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" ht="12" customHeight="1">
       <c r="C78" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
@@ -13048,154 +13904,154 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" ht="12" customHeight="1">
       <c r="C79" t="inlineStr">
         <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" ht="12" customHeight="1">
+      <c r="C80" t="inlineStr">
+        <is>
           <t>VITALY</t>
         </is>
       </c>
-      <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" ht="12" customHeight="1">
-      <c r="A80" s="54" t="n"/>
-      <c r="B80" s="54" t="n"/>
-      <c r="C80" s="55" t="inlineStr">
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="12" customHeight="1">
+      <c r="A81" s="54" t="n"/>
+      <c r="B81" s="54" t="n"/>
+      <c r="C81" s="55" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D80" s="54" t="n">
+      <c r="D81" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="E80" s="54" t="n">
+      <c r="E81" s="54" t="n">
         <v>21</v>
       </c>
-      <c r="F80" s="54" t="n">
-        <v>20</v>
-      </c>
-      <c r="G80" s="54" t="n">
+      <c r="F81" s="54" t="n">
+        <v>23</v>
+      </c>
+      <c r="G81" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="H80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="54" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q80" s="54" t="n"/>
-    </row>
-    <row r="81" ht="12" customHeight="1">
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>ADOBE</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>3</v>
-      </c>
+      <c r="H81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="54" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q81" s="54" t="n"/>
     </row>
     <row r="82" ht="12" customHeight="1">
       <c r="C82" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -13241,17 +14097,17 @@
     <row r="83" ht="12" customHeight="1">
       <c r="C83" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" s="56" t="n">
         <v>0</v>
@@ -13281,23 +14137,23 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" ht="12" customHeight="1">
       <c r="C84" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="56" t="n">
         <v>0</v>
@@ -13327,13 +14183,13 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" ht="12" customHeight="1">
       <c r="C85" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -13379,7 +14235,7 @@
     <row r="86" ht="12" customHeight="1">
       <c r="C86" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -13389,9 +14245,9 @@
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
@@ -13419,69 +14275,69 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" ht="12" customHeight="1">
       <c r="C87" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
         <v>2</v>
-      </c>
-      <c r="E87" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" t="n">
-        <v>3</v>
-      </c>
-      <c r="G87" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="88" ht="12" customHeight="1">
       <c r="C88" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G88" s="56" t="n">
         <v>0</v>
@@ -13511,23 +14367,23 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" ht="12" customHeight="1">
       <c r="C89" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="56" t="n">
         <v>0</v>
@@ -13557,66 +14413,66 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" ht="12" customHeight="1">
       <c r="C90" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>2</v>
       </c>
       <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
         <v>6</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="91" ht="12" customHeight="1">
       <c r="C91" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
@@ -13649,13 +14505,13 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" ht="12" customHeight="1">
       <c r="C92" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -13667,8 +14523,8 @@
       <c r="F92" t="n">
         <v>1</v>
       </c>
-      <c r="G92" t="n">
-        <v>1</v>
+      <c r="G92" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -13695,25 +14551,25 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" ht="12" customHeight="1">
       <c r="C93" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
-      </c>
-      <c r="G93" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
         <v>1</v>
       </c>
       <c r="H93" t="n">
@@ -13741,26 +14597,26 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" ht="12" customHeight="1">
       <c r="C94" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G94" s="56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -13787,13 +14643,13 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" ht="12" customHeight="1">
       <c r="C95" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -13837,102 +14693,194 @@
       </c>
     </row>
     <row r="96" ht="12" customHeight="1">
-      <c r="A96" s="54" t="n"/>
-      <c r="B96" s="54" t="n"/>
-      <c r="C96" s="55" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SYNCWITH</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" ht="12" customHeight="1">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" ht="12" customHeight="1">
+      <c r="A98" s="54" t="n"/>
+      <c r="B98" s="54" t="n"/>
+      <c r="C98" s="55" t="inlineStr">
         <is>
           <t>Uncategorized Expenses</t>
         </is>
       </c>
-      <c r="D96" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="54" t="n">
+      <c r="D98" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" s="54" t="n"/>
-    </row>
-    <row r="97" ht="12" customHeight="1">
-      <c r="A97" s="54" t="n"/>
-      <c r="B97" s="55" t="inlineStr">
+      <c r="Q98" s="54" t="n"/>
+    </row>
+    <row r="99" ht="12" customHeight="1">
+      <c r="A99" s="54" t="n"/>
+      <c r="B99" s="55" t="inlineStr">
         <is>
           <t>Currency Adjustment</t>
         </is>
       </c>
-      <c r="C97" s="54" t="n"/>
-      <c r="D97" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="54" t="n">
+      <c r="C99" s="54" t="n"/>
+      <c r="D99" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="Q97" s="54" t="n"/>
+      <c r="Q99" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14325,51 +15273,51 @@
         </is>
       </c>
       <c r="D8" s="47">
-        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="E8" s="47">
-        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="F8" s="47">
-        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="G8" s="47">
-        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="H8" s="47">
-        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="I8" s="47">
-        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="J8" s="47">
-        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="K8" s="47">
-        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="L8" s="47">
-        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="M8" s="47">
-        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="N8" s="47">
-        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="O8" s="47">
-        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O89)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="P8" s="47">
@@ -14728,51 +15676,51 @@
         </is>
       </c>
       <c r="D16" s="47">
-        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="E16" s="47">
-        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="F16" s="47">
-        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="G16" s="47">
-        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="H16" s="47">
-        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="I16" s="47">
-        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="J16" s="47">
-        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="K16" s="47">
-        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="L16" s="47">
-        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="M16" s="47">
-        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="N16" s="47">
-        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="O16" s="47">
-        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O89)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="P16" s="47">
@@ -15041,7 +15989,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-04T10:00:08Z</t>
+          <t>2026-04-10T09:47:54Z</t>
         </is>
       </c>
     </row>
@@ -15052,7 +16000,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" ht="12" customHeight="1">
@@ -15062,7 +16010,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
@@ -15072,7 +16020,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -15082,7 +16030,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -15099,7 +16047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16503,7 +17451,7 @@
         </is>
       </c>
       <c r="E30" s="47" t="n">
-        <v>384.35</v>
+        <v>1520.56</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -16519,7 +17467,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="47" t="n">
-        <v>384.35</v>
+        <v>1520.56</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -16542,16 +17490,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E31" s="47" t="n">
-        <v>2177.17</v>
+        <v>25.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -16567,7 +17515,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="47" t="n">
-        <v>2177.17</v>
+        <v>25.5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -16590,16 +17538,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E32" s="47" t="n">
-        <v>16104.78</v>
+        <v>6557.08</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -16615,7 +17563,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="47" t="n">
-        <v>16104.78</v>
+        <v>6557.08</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -16638,16 +17586,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E33" s="47" t="n">
-        <v>5016.62</v>
+        <v>31818.42</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -16663,7 +17611,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="47" t="n">
-        <v>5016.62</v>
+        <v>31818.42</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -16686,16 +17634,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E34" s="47" t="n">
-        <v>2032.98</v>
+        <v>10154.56</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -16711,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="47" t="n">
-        <v>2032.98</v>
+        <v>10154.56</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -16720,6 +17668,102 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="12" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E35" s="47" t="n">
+        <v>4700.54</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H35" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="47" t="n">
+        <v>4700.54</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>finance.ventas_pyg</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="12" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="E36" s="47" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H36" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="47" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>finance.ventas_pyg</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16735,7 +17779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17045,6 +18089,62 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="12" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>1277.93</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H7" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>1277.93</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="K7" s="49" t="inlineStr">
+        <is>
+          <t>2026-0018</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sizgdxMBUT_B7ZP3pPW8o5AjPDT-reZn/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'P&amp;G-SL'!A1" display="&lt;- Volver a P&amp;G-SL"/>
@@ -17052,6 +18152,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17548,7 +18649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18082,6 +19183,230 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QHANDS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>renting_cnc</t>
+        </is>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H11" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="47" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="K11" s="49" t="inlineStr">
+        <is>
+          <t>2026-0020</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1cecAxU56GNtGgMfgA6Ftf1gfGiXJDd3S/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>595.59</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H12" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="47" t="n">
+        <v>595.59</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="K12" s="49" t="inlineStr">
+        <is>
+          <t>2026-0019</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1HxjVp-Wv6lXooijCdy9-Z79LhGmFJwc2/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Inc</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E13" s="47" t="n">
+        <v>7586.05</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H13" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="47" t="n">
+        <v>7586.05</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>documents:shared_services</t>
+        </is>
+      </c>
+      <c r="K13" s="49" t="inlineStr">
+        <is>
+          <t>2026-0017</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ixVdpnGpB3KUF2QQIt94W1I4J6yD6ybZ/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="12" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ltd</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>14144.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H14" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="47" t="n">
+        <v>14144.1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>documents:shared_services</t>
+        </is>
+      </c>
+      <c r="K14" s="49" t="inlineStr">
+        <is>
+          <t>2026-0016</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1KdK-Ik0l5-TAvrDmyV47ighudMtGRrKE/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'P&amp;G-SL'!A1" display="&lt;- Volver a P&amp;G-SL"/>
@@ -18093,6 +19418,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18104,7 +19433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N171"/>
+  <dimension ref="A1:N180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25867,22 +27196,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CORREOS</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" s="47" t="n">
-        <v>193.8</v>
+        <v>191.4</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -25898,7 +27227,7 @@
         <v>1</v>
       </c>
       <c r="K125" s="47" t="n">
-        <v>193.8</v>
+        <v>191.4</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -25907,12 +27236,12 @@
       </c>
       <c r="M125" s="49" t="inlineStr">
         <is>
-          <t>4004641446</t>
+          <t>ES-2026-11348</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19BOJcU-tZOdXNewpB9MmZXKbUeYoLmQW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Kf3zLbAifsK47hwsfDtdiya2nTjoZhbc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25939,12 +27268,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CORREOSCAN</t>
+          <t>CORREOS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" s="47" t="n">
-        <v>8.83</v>
+        <v>193.8</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -25960,7 +27289,7 @@
         <v>1</v>
       </c>
       <c r="K126" s="47" t="n">
-        <v>8.83</v>
+        <v>193.8</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -25969,12 +27298,12 @@
       </c>
       <c r="M126" s="49" t="inlineStr">
         <is>
-          <t>4004641447</t>
+          <t>4004641446</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OSsPTK_eKr03kWPWfsduaZWbO-PcRSKN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19BOJcU-tZOdXNewpB9MmZXKbUeYoLmQW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25996,17 +27325,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>CORREOSCAN</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" s="47" t="n">
-        <v>2646.66</v>
+        <v>8.83</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -26022,7 +27351,7 @@
         <v>1</v>
       </c>
       <c r="K127" s="47" t="n">
-        <v>2646.66</v>
+        <v>8.83</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -26031,12 +27360,12 @@
       </c>
       <c r="M127" s="49" t="inlineStr">
         <is>
-          <t>26-0463</t>
+          <t>4004641447</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d9bGOdNerfRkG8hm-9tNwNLOClNoUKV1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1OSsPTK_eKr03kWPWfsduaZWbO-PcRSKN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26068,7 +27397,7 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" s="47" t="n">
-        <v>2854.58</v>
+        <v>2646.66</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -26084,7 +27413,7 @@
         <v>1</v>
       </c>
       <c r="K128" s="47" t="n">
-        <v>2854.58</v>
+        <v>2646.66</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -26093,12 +27422,12 @@
       </c>
       <c r="M128" s="49" t="inlineStr">
         <is>
-          <t>26-0548</t>
+          <t>26-0463</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RN40IgZT0khKxDgZ1TciqcREU1AzC6iG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d9bGOdNerfRkG8hm-9tNwNLOClNoUKV1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26115,22 +27444,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" s="47" t="n">
-        <v>13.11</v>
+        <v>2854.58</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -26146,7 +27475,7 @@
         <v>1</v>
       </c>
       <c r="K129" s="47" t="n">
-        <v>13.11</v>
+        <v>2854.58</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -26155,12 +27484,12 @@
       </c>
       <c r="M129" s="49" t="inlineStr">
         <is>
-          <t>4046950709</t>
+          <t>26-0548</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mhP1xnzmk8CIu8lzS9UTKi1YVgQ0j5vD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RN40IgZT0khKxDgZ1TciqcREU1AzC6iG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26177,22 +27506,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" s="47" t="n">
-        <v>21.99</v>
+        <v>14170.85</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -26208,7 +27537,7 @@
         <v>1</v>
       </c>
       <c r="K130" s="47" t="n">
-        <v>21.99</v>
+        <v>14170.85</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -26217,12 +27546,12 @@
       </c>
       <c r="M130" s="49" t="inlineStr">
         <is>
-          <t>4048729358</t>
+          <t>20260150</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EeQh_f0ge3L2vpmoZhGqULVvQDnFYlXt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Fys_Ke3o0S3pZkqtEQkaOmeaEm-sTj0X/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26244,21 +27573,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>eu</t>
-        </is>
-      </c>
+          <t>GODADDY</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" s="47" t="n">
-        <v>24360.27</v>
+        <v>13.11</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -26274,7 +27599,7 @@
         <v>1</v>
       </c>
       <c r="K131" s="47" t="n">
-        <v>24360.27</v>
+        <v>13.11</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -26283,12 +27608,12 @@
       </c>
       <c r="M131" s="49" t="inlineStr">
         <is>
-          <t>5538547928</t>
+          <t>4046950709</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s7eUjqGV_ux0WxJrpYLtGKjjOS3f9F_q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mhP1xnzmk8CIu8lzS9UTKi1YVgQ0j5vD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26310,21 +27635,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>uk</t>
-        </is>
-      </c>
+          <t>GODADDY</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" s="47" t="n">
-        <v>5956.59</v>
+        <v>21.99</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -26340,7 +27661,7 @@
         <v>1</v>
       </c>
       <c r="K132" s="47" t="n">
-        <v>5956.59</v>
+        <v>21.99</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -26349,12 +27670,12 @@
       </c>
       <c r="M132" s="49" t="inlineStr">
         <is>
-          <t>5538547928</t>
+          <t>4048729358</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s7eUjqGV_ux0WxJrpYLtGKjjOS3f9F_q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EeQh_f0ge3L2vpmoZhGqULVvQDnFYlXt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26386,11 +27707,11 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="G133" s="47" t="n">
-        <v>3341.56</v>
+        <v>24360.27</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -26406,7 +27727,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="47" t="n">
-        <v>3341.56</v>
+        <v>24360.27</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -26442,17 +27763,21 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
       <c r="G134" s="47" t="n">
-        <v>210.6</v>
+        <v>5956.59</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -26468,7 +27793,7 @@
         <v>1</v>
       </c>
       <c r="K134" s="47" t="n">
-        <v>210.6</v>
+        <v>5956.59</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -26477,12 +27802,12 @@
       </c>
       <c r="M134" s="49" t="inlineStr">
         <is>
-          <t>5528949048</t>
+          <t>5538547928</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l-tObm8vyP3XyPss2x7ZU0ypwypzolZi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s7eUjqGV_ux0WxJrpYLtGKjjOS3f9F_q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26504,21 +27829,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G135" s="47" t="n">
-        <v>126.4</v>
+        <v>3341.56</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -26527,10 +27856,10 @@
         </is>
       </c>
       <c r="J135" s="48" t="n">
-        <v>0.86971647</v>
+        <v>1</v>
       </c>
       <c r="K135" s="47" t="n">
-        <v>109.93</v>
+        <v>3341.56</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -26539,12 +27868,12 @@
       </c>
       <c r="M135" s="49" t="inlineStr">
         <is>
-          <t>INC-03-2026-64889</t>
+          <t>5538547928</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1r5NeAkt6BuK7stM77wMD2GmwfOkmyuaE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s7eUjqGV_ux0WxJrpYLtGKjjOS3f9F_q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26566,21 +27895,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HANNUN</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
+          <t>GOOGLEWORKSPACE</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" s="47" t="n">
-        <v>30</v>
+        <v>210.6</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -26596,7 +27921,7 @@
         <v>1</v>
       </c>
       <c r="K136" s="47" t="n">
-        <v>30</v>
+        <v>210.6</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -26605,12 +27930,12 @@
       </c>
       <c r="M136" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-010337</t>
+          <t>5528949048</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jBhJD7kS5_SPwJKWbOaHjrF8mX4mpiT8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1l-tObm8vyP3XyPss2x7ZU0ypwypzolZi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26637,16 +27962,16 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" s="47" t="n">
-        <v>182.45</v>
+        <v>126.4</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -26655,10 +27980,10 @@
         </is>
       </c>
       <c r="J137" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K137" s="47" t="n">
-        <v>182.45</v>
+        <v>109.93</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -26667,12 +27992,12 @@
       </c>
       <c r="M137" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7472</t>
+          <t>INC-03-2026-64889</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nWo-mNGMmMRAWJEGmVLJaMtqo73kBgzv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r5NeAkt6BuK7stM77wMD2GmwfOkmyuaE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26694,17 +28019,21 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
       <c r="G138" s="47" t="n">
-        <v>339</v>
+        <v>30</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -26720,7 +28049,7 @@
         <v>1</v>
       </c>
       <c r="K138" s="47" t="n">
-        <v>339</v>
+        <v>30</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -26729,12 +28058,12 @@
       </c>
       <c r="M138" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7629</t>
+          <t>VTA/26-010337</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CqOn2Zx8mbhJOVhiMIiGbOghQnA3vTDp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jBhJD7kS5_SPwJKWbOaHjrF8mX4mpiT8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26756,17 +28085,21 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
       <c r="G139" s="47" t="n">
-        <v>60.44</v>
+        <v>175</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -26782,7 +28115,7 @@
         <v>1</v>
       </c>
       <c r="K139" s="47" t="n">
-        <v>60.44</v>
+        <v>175</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -26791,12 +28124,12 @@
       </c>
       <c r="M139" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7709</t>
+          <t>VTA/26-012333</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ECBhz1VCwbBVoxwkdm3YFSwEGxpN8nXX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y_VFTA5on6ReO79xvnlu0N3xL-BbnpEM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26818,17 +28151,21 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
       <c r="G140" s="47" t="n">
-        <v>8.83</v>
+        <v>1165.1</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -26844,7 +28181,7 @@
         <v>1</v>
       </c>
       <c r="K140" s="47" t="n">
-        <v>8.83</v>
+        <v>1165.1</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -26853,12 +28190,12 @@
       </c>
       <c r="M140" s="49" t="inlineStr">
         <is>
-          <t>MC260003336170</t>
+          <t>VTA/26-012334</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18aHMUoONC6SlndhHYF_AWRN3TCOoVrvg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1BXJcbamEE34UrEHgJabkn3cuDfiFSgXJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26880,21 +28217,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>METAADS</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>eu</t>
-        </is>
-      </c>
+          <t>KONVOAI</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" s="47" t="n">
-        <v>17635.61</v>
+        <v>182.45</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -26910,7 +28243,7 @@
         <v>1</v>
       </c>
       <c r="K141" s="47" t="n">
-        <v>17635.61</v>
+        <v>182.45</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -26919,12 +28252,12 @@
       </c>
       <c r="M141" s="49" t="inlineStr">
         <is>
-          <t>251912684</t>
+          <t>B5F7DF3C-7472</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nWo-mNGMmMRAWJEGmVLJaMtqo73kBgzv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26946,21 +28279,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>METAADS</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>uk</t>
-        </is>
-      </c>
+          <t>KONVOAI</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" s="47" t="n">
-        <v>2970.18</v>
+        <v>339</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -26976,7 +28305,7 @@
         <v>1</v>
       </c>
       <c r="K142" s="47" t="n">
-        <v>2970.18</v>
+        <v>339</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -26985,12 +28314,12 @@
       </c>
       <c r="M142" s="49" t="inlineStr">
         <is>
-          <t>251912684</t>
+          <t>B5F7DF3C-7629</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CqOn2Zx8mbhJOVhiMIiGbOghQnA3vTDp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27012,21 +28341,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>METAADS</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>us</t>
-        </is>
-      </c>
+          <t>KONVOAI</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" s="47" t="n">
-        <v>1317.27</v>
+        <v>60.44</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -27042,7 +28367,7 @@
         <v>1</v>
       </c>
       <c r="K143" s="47" t="n">
-        <v>1317.27</v>
+        <v>60.44</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -27051,12 +28376,12 @@
       </c>
       <c r="M143" s="49" t="inlineStr">
         <is>
-          <t>251912684</t>
+          <t>B5F7DF3C-7709</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ECBhz1VCwbBVoxwkdm3YFSwEGxpN8nXX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27083,12 +28408,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" s="47" t="n">
-        <v>30.87</v>
+        <v>8.83</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -27104,7 +28429,7 @@
         <v>1</v>
       </c>
       <c r="K144" s="47" t="n">
-        <v>30.87</v>
+        <v>8.83</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -27113,12 +28438,12 @@
       </c>
       <c r="M144" s="49" t="inlineStr">
         <is>
-          <t>G146754373</t>
+          <t>MC260003336170</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DCPq5CCQbxKn8xbE5ConsRttwki8sRoJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18aHMUoONC6SlndhHYF_AWRN3TCOoVrvg/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27140,17 +28465,21 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
       <c r="G145" s="47" t="n">
-        <v>45.7</v>
+        <v>17635.61</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -27166,7 +28495,7 @@
         <v>1</v>
       </c>
       <c r="K145" s="47" t="n">
-        <v>45.7</v>
+        <v>17635.61</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -27175,12 +28504,12 @@
       </c>
       <c r="M145" s="49" t="inlineStr">
         <is>
-          <t>G147511406</t>
+          <t>251912684</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j0AP8BcSvjbMkHqbG0jNHzXuXksgaBTp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27202,25 +28531,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>api_usage</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G146" s="47" t="n">
-        <v>15</v>
+        <v>2970.18</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -27229,10 +28558,10 @@
         </is>
       </c>
       <c r="J146" s="48" t="n">
-        <v>0.86971647</v>
+        <v>1</v>
       </c>
       <c r="K146" s="47" t="n">
-        <v>13.05</v>
+        <v>2970.18</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -27241,12 +28570,12 @@
       </c>
       <c r="M146" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0008</t>
+          <t>251912684</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14mLVYewapKRBwsNP7f6wLOc4WRmROQLm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27263,22 +28592,26 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PRESSING</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G147" s="47" t="n">
-        <v>30382.03</v>
+        <v>1317.27</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -27294,7 +28627,7 @@
         <v>1</v>
       </c>
       <c r="K147" s="47" t="n">
-        <v>30382.03</v>
+        <v>1317.27</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -27303,12 +28636,12 @@
       </c>
       <c r="M147" s="49" t="inlineStr">
         <is>
-          <t>FAC/2026/26100002919</t>
+          <t>251912684</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NnctdjrWo_YQUOWmOChF9VEkLKCvwH7r/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27325,22 +28658,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>PRESSING</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" s="47" t="n">
-        <v>-15135.51</v>
+        <v>30.87</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -27356,7 +28689,7 @@
         <v>1</v>
       </c>
       <c r="K148" s="47" t="n">
-        <v>-15135.51</v>
+        <v>30.87</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -27365,12 +28698,12 @@
       </c>
       <c r="M148" s="49" t="inlineStr">
         <is>
-          <t>REC/2026/26200000052</t>
+          <t>G146754373</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AS6ZaTkoyH52MXQbp1lIDdFsAOEBnPum/view</t>
+          <t>https://drive.google.com/file/d/1DCPq5CCQbxKn8xbE5ConsRttwki8sRoJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27397,12 +28730,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" s="47" t="n">
-        <v>134</v>
+        <v>45.7</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -27418,7 +28751,7 @@
         <v>1</v>
       </c>
       <c r="K149" s="47" t="n">
-        <v>134</v>
+        <v>45.7</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -27427,12 +28760,12 @@
       </c>
       <c r="M149" s="49" t="inlineStr">
         <is>
-          <t>217905</t>
+          <t>G147511406</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1q5GM5mcOxTlAfTEBbnsDgygc2l8igChV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1j0AP8BcSvjbMkHqbG0jNHzXuXksgaBTp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27459,12 +28792,16 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>api_usage</t>
+        </is>
+      </c>
       <c r="G150" s="47" t="n">
-        <v>21.36</v>
+        <v>15</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -27480,7 +28817,7 @@
         <v>0.86971647</v>
       </c>
       <c r="K150" s="47" t="n">
-        <v>18.58</v>
+        <v>13.05</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -27489,12 +28826,12 @@
       </c>
       <c r="M150" s="49" t="inlineStr">
         <is>
-          <t>1602C2F5-0017</t>
+          <t>BZHJNTUB0008</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_zSaGhAEICAUBmqreT7FKVxXgv2-r3jW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14mLVYewapKRBwsNP7f6wLOc4WRmROQLm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27511,22 +28848,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>PRESSING</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" s="47" t="n">
-        <v>436.38</v>
+        <v>30382.03</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -27542,7 +28879,7 @@
         <v>1</v>
       </c>
       <c r="K151" s="47" t="n">
-        <v>436.38</v>
+        <v>30382.03</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -27551,12 +28888,12 @@
       </c>
       <c r="M151" s="49" t="inlineStr">
         <is>
-          <t>RVR-17393</t>
+          <t>FAC/2026/26100002919</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CWhfJHSOw1n7f9t5k-dWx1KXNq0OtlHl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1NnctdjrWo_YQUOWmOChF9VEkLKCvwH7r/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27573,22 +28910,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>PRESSING</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" s="47" t="n">
-        <v>299.89</v>
+        <v>-15135.51</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -27604,7 +28941,7 @@
         <v>1</v>
       </c>
       <c r="K152" s="47" t="n">
-        <v>299.89</v>
+        <v>-15135.51</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -27613,12 +28950,12 @@
       </c>
       <c r="M152" s="49" t="inlineStr">
         <is>
-          <t>RVR-18216</t>
+          <t>REC/2026/26200000052</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ugF3jSpFNoCK5W7nlv4RnQWYri-rwsCH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AS6ZaTkoyH52MXQbp1lIDdFsAOEBnPum/view</t>
         </is>
       </c>
     </row>
@@ -27645,12 +28982,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" s="47" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -27666,7 +29003,7 @@
         <v>1</v>
       </c>
       <c r="K153" s="47" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -27675,12 +29012,12 @@
       </c>
       <c r="M153" s="49" t="inlineStr">
         <is>
-          <t>RVR-18566</t>
+          <t>217905</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dHhK1m1wSqKZeeNradd6kO_U1yP4OEZx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1q5GM5mcOxTlAfTEBbnsDgygc2l8igChV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27707,12 +29044,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" s="47" t="n">
-        <v>3223.43</v>
+        <v>21.36</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -27728,7 +29065,7 @@
         <v>0.86971647</v>
       </c>
       <c r="K154" s="47" t="n">
-        <v>2803.47</v>
+        <v>18.58</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -27737,12 +29074,12 @@
       </c>
       <c r="M154" s="49" t="inlineStr">
         <is>
-          <t>506718743</t>
+          <t>1602C2F5-0017</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZCs5X4Qp9kY8mI50ovA19IzFEuYf6xco/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_zSaGhAEICAUBmqreT7FKVxXgv2-r3jW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27764,17 +29101,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" s="47" t="n">
-        <v>15</v>
+        <v>436.38</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -27790,7 +29127,7 @@
         <v>1</v>
       </c>
       <c r="K155" s="47" t="n">
-        <v>15</v>
+        <v>436.38</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -27799,12 +29136,12 @@
       </c>
       <c r="M155" s="49" t="inlineStr">
         <is>
-          <t>7/800</t>
+          <t>RVR-17393</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qLKvi2Ja2apUNKYZBiLqZTt00IfYF7J2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CWhfJHSOw1n7f9t5k-dWx1KXNq0OtlHl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27821,22 +29158,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" s="47" t="n">
-        <v>723.1799999999999</v>
+        <v>299.89</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -27852,7 +29189,7 @@
         <v>1</v>
       </c>
       <c r="K156" s="47" t="n">
-        <v>723.1799999999999</v>
+        <v>299.89</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -27861,12 +29198,12 @@
       </c>
       <c r="M156" s="49" t="inlineStr">
         <is>
-          <t>327127415</t>
+          <t>RVR-18216</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1szeFukWcwJsTpYUKLKIKWZXLhy2sel8E/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ugF3jSpFNoCK5W7nlv4RnQWYri-rwsCH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27883,22 +29220,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" s="47" t="n">
-        <v>401.71</v>
+        <v>79</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -27914,7 +29251,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="47" t="n">
-        <v>401.71</v>
+        <v>79</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -27923,12 +29260,12 @@
       </c>
       <c r="M157" s="49" t="inlineStr">
         <is>
-          <t>327158453</t>
+          <t>RVR-18566</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1w16eZ2iuW4dPbkomePY18LR7CPlxsdYp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dHhK1m1wSqKZeeNradd6kO_U1yP4OEZx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27945,26 +29282,26 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" s="47" t="n">
-        <v>580.51</v>
+        <v>3223.43</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -27973,10 +29310,10 @@
         </is>
       </c>
       <c r="J158" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K158" s="47" t="n">
-        <v>580.51</v>
+        <v>2803.47</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -27985,12 +29322,12 @@
       </c>
       <c r="M158" s="49" t="inlineStr">
         <is>
-          <t>327190672</t>
+          <t>506718743</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YGt6D24m8-UdGBL3aaHOe0wVC7k4qghi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZCs5X4Qp9kY8mI50ovA19IzFEuYf6xco/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28007,26 +29344,26 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" s="47" t="n">
-        <v>7.91</v>
+        <v>24.99</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -28035,10 +29372,10 @@
         </is>
       </c>
       <c r="J159" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K159" s="47" t="n">
-        <v>7.91</v>
+        <v>21.73</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -28047,12 +29384,12 @@
       </c>
       <c r="M159" s="49" t="inlineStr">
         <is>
-          <t>838283238</t>
+          <t>TADGCDFS-0001</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1enWtjyf2SUswvIm0_3r2ARUO4Nc_9Jd0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PjQXXRgJWle6bvVGYUn8W3Swp9IqcBqL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28074,21 +29411,21 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" s="47" t="n">
-        <v>369</v>
+        <v>24.99</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -28097,10 +29434,10 @@
         </is>
       </c>
       <c r="J160" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K160" s="47" t="n">
-        <v>369</v>
+        <v>21.73</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -28109,12 +29446,12 @@
       </c>
       <c r="M160" s="49" t="inlineStr">
         <is>
-          <t>IFC2603-18831</t>
+          <t>TADGCDFS-0002</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YylC1UsF8Mmxn_K1BFQWDm5IBpU5pT4S/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dZC3fsBfen5iERm3x2JFrd1LGddt0qLb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28141,16 +29478,16 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" s="47" t="n">
-        <v>440</v>
+        <v>24.99</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -28159,10 +29496,10 @@
         </is>
       </c>
       <c r="J161" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K161" s="47" t="n">
-        <v>440</v>
+        <v>21.73</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -28171,19 +29508,19 @@
       </c>
       <c r="M161" s="49" t="inlineStr">
         <is>
-          <t>OQXBYXMP-0006</t>
+          <t>TADGCDFS-0003</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Dfe3TUTMjwwXhP0sW7OA-brj3bzdreVa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19CqsBdkfVuCtWYJwUtZxWcPjUVgdtwXa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="162" ht="12" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -28198,21 +29535,21 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" s="47" t="n">
-        <v>32.14</v>
+        <v>15</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -28221,10 +29558,10 @@
         </is>
       </c>
       <c r="J162" s="48" t="n">
-        <v>0.86767896</v>
+        <v>1</v>
       </c>
       <c r="K162" s="47" t="n">
-        <v>27.89</v>
+        <v>15</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -28233,19 +29570,19 @@
       </c>
       <c r="M162" s="49" t="inlineStr">
         <is>
-          <t>1602C2F5-0018</t>
+          <t>7/800</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CAMDKbnRLAc0BtTnaayjMCU0RGZ6dmCJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qLKvi2Ja2apUNKYZBiLqZTt00IfYF7J2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="163" ht="12" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -28255,22 +29592,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" s="47" t="n">
-        <v>135.59</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -28286,7 +29623,7 @@
         <v>1</v>
       </c>
       <c r="K163" s="47" t="n">
-        <v>135.59</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -28295,19 +29632,19 @@
       </c>
       <c r="M163" s="49" t="inlineStr">
         <is>
-          <t>RVR-19093</t>
+          <t>327127415</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1a9PDsbMBEl6jr1J063Bas9xJ16j0K-Vt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1szeFukWcwJsTpYUKLKIKWZXLhy2sel8E/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="164" ht="12" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -28322,17 +29659,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" s="47" t="n">
-        <v>13737</v>
+        <v>401.71</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -28348,20 +29685,28 @@
         <v>1</v>
       </c>
       <c r="K164" s="47" t="n">
-        <v>13737</v>
+        <v>401.71</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M164" s="49" t="inlineStr">
+        <is>
+          <t>327158453</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1w16eZ2iuW4dPbkomePY18LR7CPlxsdYp/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="12" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -28376,17 +29721,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" s="47" t="n">
-        <v>16662</v>
+        <v>580.51</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -28402,15 +29747,23 @@
         <v>1</v>
       </c>
       <c r="K165" s="47" t="n">
-        <v>16662</v>
+        <v>580.51</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M165" s="49" t="inlineStr">
+        <is>
+          <t>327190672</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YGt6D24m8-UdGBL3aaHOe0wVC7k4qghi/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="12" customHeight="1">
       <c r="A166" t="inlineStr">
@@ -28430,17 +29783,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" s="47" t="n">
-        <v>14544</v>
+        <v>7.91</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -28456,20 +29809,28 @@
         <v>1</v>
       </c>
       <c r="K166" s="47" t="n">
-        <v>14544</v>
+        <v>7.91</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M166" s="49" t="inlineStr">
+        <is>
+          <t>838283238</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1enWtjyf2SUswvIm0_3r2ARUO4Nc_9Jd0/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="12" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -28484,17 +29845,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" s="47" t="n">
-        <v>14731.84</v>
+        <v>369</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -28510,20 +29871,28 @@
         <v>1</v>
       </c>
       <c r="K167" s="47" t="n">
-        <v>14731.84</v>
+        <v>369</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M167" s="49" t="inlineStr">
+        <is>
+          <t>IFC2603-18831</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YylC1UsF8Mmxn_K1BFQWDm5IBpU5pT4S/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="12" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -28538,17 +29907,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" s="47" t="n">
-        <v>14915.68</v>
+        <v>440</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -28564,20 +29933,28 @@
         <v>1</v>
       </c>
       <c r="K168" s="47" t="n">
-        <v>14915.68</v>
+        <v>440</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M168" s="49" t="inlineStr">
+        <is>
+          <t>OQXBYXMP-0006</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Dfe3TUTMjwwXhP0sW7OA-brj3bzdreVa/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="12" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -28592,17 +29969,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" s="47" t="n">
-        <v>15349.42</v>
+        <v>808.08</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -28618,20 +29995,28 @@
         <v>1</v>
       </c>
       <c r="K169" s="47" t="n">
-        <v>15349.42</v>
+        <v>808.08</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M169" s="49" t="inlineStr">
+        <is>
+          <t>F01033/26</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1YU4Rv32gQWRnZltbnXYoiABaHUadZkPC/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="12" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -28646,25 +30031,21 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Otros gastos enero 2026</t>
-        </is>
-      </c>
+          <t>RAILWAY</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" s="47" t="n">
-        <v>411.87</v>
+        <v>32.14</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -28673,76 +30054,590 @@
         </is>
       </c>
       <c r="J170" s="48" t="n">
-        <v>1</v>
+        <v>0.85579803</v>
       </c>
       <c r="K170" s="47" t="n">
-        <v>411.87</v>
+        <v>27.51</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M170" s="49" t="inlineStr">
+        <is>
+          <t>1602C2F5-0018</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1CAMDKbnRLAc0BtTnaayjMCU0RGZ6dmCJ/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="12" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" s="47" t="n">
+        <v>135.59</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J171" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" s="47" t="n">
+        <v>135.59</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M171" s="49" t="inlineStr">
+        <is>
+          <t>RVR-19093</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1a9PDsbMBEl6jr1J063Bas9xJ16j0K-Vt/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="12" customHeight="1">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J172" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M172" s="49" t="inlineStr">
+        <is>
+          <t>7/1074</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11QFEdz-ALQYNgRguLCU4q390nTPxudFV/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="12" customHeight="1">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" s="47" t="n">
+        <v>13737</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J173" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" s="47" t="n">
+        <v>13737</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+    </row>
+    <row r="174" ht="12" customHeight="1">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>202602</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" s="47" t="n">
+        <v>16662</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J174" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K174" s="47" t="n">
+        <v>16662</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+    </row>
+    <row r="175" ht="12" customHeight="1">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" s="47" t="n">
+        <v>14544</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J175" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K175" s="47" t="n">
+        <v>14544</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+    </row>
+    <row r="176" ht="12" customHeight="1">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" s="47" t="n">
+        <v>14731.84</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J176" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" s="47" t="n">
+        <v>14731.84</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+    </row>
+    <row r="177" ht="12" customHeight="1">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" s="47" t="n">
+        <v>14915.68</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J177" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" s="47" t="n">
+        <v>14915.68</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+    </row>
+    <row r="178" ht="12" customHeight="1">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" s="47" t="n">
+        <v>15349.42</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J178" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" s="47" t="n">
+        <v>15349.42</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+    </row>
+    <row r="179" ht="12" customHeight="1">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
         <is>
           <t>otros_gastos</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>OTROSGASTOS</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Otros gastos enero 2026</t>
+        </is>
+      </c>
+      <c r="G179" s="47" t="n">
+        <v>411.87</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J179" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" s="47" t="n">
+        <v>411.87</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+    </row>
+    <row r="180" ht="12" customHeight="1">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
         <is>
           <t>Otros gastos febrero 2026</t>
         </is>
       </c>
-      <c r="G171" s="47" t="n">
+      <c r="G180" s="47" t="n">
         <v>554.46</v>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J171" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K171" s="47" t="n">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J180" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" s="47" t="n">
         <v>554.46</v>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>otros_gastos</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28906,6 +30801,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M161" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M162" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M163" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M164" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M165" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M167" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M168" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29248,7 +31152,7 @@
         </is>
       </c>
       <c r="D9" s="47" t="n">
-        <v>212.13</v>
+        <v>381.67</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -29264,7 +31168,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="47" t="n">
-        <v>212.13</v>
+        <v>381.67</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -29289,7 +31193,7 @@
         </is>
       </c>
       <c r="D10" s="47" t="n">
-        <v>222.56</v>
+        <v>566.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -29305,7 +31209,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="47" t="n">
-        <v>222.56</v>
+        <v>566.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>

--- a/output/spreadsheet/pyg_sl_2026.xlsx
+++ b/output/spreadsheet/pyg_sl_2026.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -852,7 +852,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 10/04/2026 11:47 h</t>
+          <t>Actualizado: 10/04/2026 12:53 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -4807,51 +4807,51 @@
       </c>
       <c r="C64" s="13" t="n"/>
       <c r="D64" s="14">
-        <f>D65+D75+D78+D90+D107</f>
+        <f>D65+D75+D78+D91+D108</f>
         <v/>
       </c>
       <c r="E64" s="14">
-        <f>E65+E75+E78+E90+E107</f>
+        <f>E65+E75+E78+E91+E108</f>
         <v/>
       </c>
       <c r="F64" s="14">
-        <f>F65+F75+F78+F90+F107</f>
+        <f>F65+F75+F78+F91+F108</f>
         <v/>
       </c>
       <c r="G64" s="14">
-        <f>G65+G75+G78+G90+G107</f>
+        <f>G65+G75+G78+G91+G108</f>
         <v/>
       </c>
       <c r="H64" s="14">
-        <f>H65+H75+H78+H90+H107</f>
+        <f>H65+H75+H78+H91+H108</f>
         <v/>
       </c>
       <c r="I64" s="14">
-        <f>I65+I75+I78+I90+I107</f>
+        <f>I65+I75+I78+I91+I108</f>
         <v/>
       </c>
       <c r="J64" s="14">
-        <f>J65+J75+J78+J90+J107</f>
+        <f>J65+J75+J78+J91+J108</f>
         <v/>
       </c>
       <c r="K64" s="14">
-        <f>K65+K75+K78+K90+K107</f>
+        <f>K65+K75+K78+K91+K108</f>
         <v/>
       </c>
       <c r="L64" s="14">
-        <f>L65+L75+L78+L90+L107</f>
+        <f>L65+L75+L78+L91+L108</f>
         <v/>
       </c>
       <c r="M64" s="14">
-        <f>M65+M75+M78+M90+M107</f>
+        <f>M65+M75+M78+M91+M108</f>
         <v/>
       </c>
       <c r="N64" s="14">
-        <f>N65+N75+N78+N90+N107</f>
+        <f>N65+N75+N78+N91+N108</f>
         <v/>
       </c>
       <c r="O64" s="14">
-        <f>O65+O75+O78+O90+O107</f>
+        <f>O65+O75+O78+O91+O108</f>
         <v/>
       </c>
       <c r="P64" s="15">
@@ -5779,51 +5779,51 @@
         </is>
       </c>
       <c r="D78" s="20">
-        <f>D79+D80+D81+D82+D86+D87+D88+D89</f>
+        <f>D79+D80+D81+D82+D83+D87+D88+D89+D90</f>
         <v/>
       </c>
       <c r="E78" s="20">
-        <f>E79+E80+E81+E82+E86+E87+E88+E89</f>
+        <f>E79+E80+E81+E82+E83+E87+E88+E89+E90</f>
         <v/>
       </c>
       <c r="F78" s="20">
-        <f>F79+F80+F81+F82+F86+F87+F88+F89</f>
+        <f>F79+F80+F81+F82+F83+F87+F88+F89+F90</f>
         <v/>
       </c>
       <c r="G78" s="20">
-        <f>G79+G80+G81+G82+G86+G87+G88+G89</f>
+        <f>G79+G80+G81+G82+G83+G87+G88+G89+G90</f>
         <v/>
       </c>
       <c r="H78" s="20">
-        <f>H79+H80+H81+H82+H86+H87+H88+H89</f>
+        <f>H79+H80+H81+H82+H83+H87+H88+H89+H90</f>
         <v/>
       </c>
       <c r="I78" s="20">
-        <f>I79+I80+I81+I82+I86+I87+I88+I89</f>
+        <f>I79+I80+I81+I82+I83+I87+I88+I89+I90</f>
         <v/>
       </c>
       <c r="J78" s="20">
-        <f>J79+J80+J81+J82+J86+J87+J88+J89</f>
+        <f>J79+J80+J81+J82+J83+J87+J88+J89+J90</f>
         <v/>
       </c>
       <c r="K78" s="20">
-        <f>K79+K80+K81+K82+K86+K87+K88+K89</f>
+        <f>K79+K80+K81+K82+K83+K87+K88+K89+K90</f>
         <v/>
       </c>
       <c r="L78" s="20">
-        <f>L79+L80+L81+L82+L86+L87+L88+L89</f>
+        <f>L79+L80+L81+L82+L83+L87+L88+L89+L90</f>
         <v/>
       </c>
       <c r="M78" s="20">
-        <f>M79+M80+M81+M82+M86+M87+M88+M89</f>
+        <f>M79+M80+M81+M82+M83+M87+M88+M89+M90</f>
         <v/>
       </c>
       <c r="N78" s="20">
-        <f>N79+N80+N81+N82+N86+N87+N88+N89</f>
+        <f>N79+N80+N81+N82+N83+N87+N88+N89+N90</f>
         <v/>
       </c>
       <c r="O78" s="20">
-        <f>O79+O80+O81+O82+O86+O87+O88+O89</f>
+        <f>O79+O80+O81+O82+O83+O87+O88+O89+O90</f>
         <v/>
       </c>
       <c r="P78" s="21">
@@ -5839,13 +5839,13 @@
     <row r="79" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            BBVACNC</t>
+          <t xml:space="preserve">            ADEPLUS</t>
         </is>
       </c>
       <c r="B79" s="4" t="n"/>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>BBVACNC</t>
+          <t>ADEPLUS</t>
         </is>
       </c>
       <c r="D79" s="5">
@@ -5909,13 +5909,13 @@
     <row r="80" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A80" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            CLARIS</t>
+          <t xml:space="preserve">            BBVACNC</t>
         </is>
       </c>
       <c r="B80" s="4" t="n"/>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>BBVACNC</t>
         </is>
       </c>
       <c r="D80" s="5">
@@ -5979,13 +5979,13 @@
     <row r="81" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            CONTASIMPLE</t>
+          <t xml:space="preserve">            CLARIS</t>
         </is>
       </c>
       <c r="B81" s="4" t="n"/>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>CONTASIMPLE</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="D81" s="5">
@@ -6049,13 +6049,13 @@
     <row r="82" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            HANNUN</t>
+          <t xml:space="preserve">            CONTASIMPLE</t>
         </is>
       </c>
       <c r="B82" s="4" t="n"/>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="D82" s="5">
@@ -6119,61 +6119,61 @@
     <row r="83" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            administration</t>
+          <t xml:space="preserve">            HANNUN</t>
         </is>
       </c>
       <c r="B83" s="4" t="n"/>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="E83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="F83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="G83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="H83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="I83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="J83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="K83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="L83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="M83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="N83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="O83" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C83)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83)</f>
         <v/>
       </c>
       <c r="P83" s="24">
@@ -6189,61 +6189,61 @@
     <row r="84" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            office</t>
+          <t xml:space="preserve">            administration</t>
         </is>
       </c>
       <c r="B84" s="4" t="n"/>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="E84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="F84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="G84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="H84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="I84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="J84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="K84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="L84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="M84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="N84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="O84" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C84)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C84)</f>
         <v/>
       </c>
       <c r="P84" s="24">
@@ -6256,64 +6256,64 @@
         </is>
       </c>
     </row>
-    <row r="85" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="85" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            services</t>
+          <t xml:space="preserve">            office</t>
         </is>
       </c>
       <c r="B85" s="4" t="n"/>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="E85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="F85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="G85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="H85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="I85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="J85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="K85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="L85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="M85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="N85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="O85" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C82,'g-expenses-sl'!$F:$F,$C85)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C85)</f>
         <v/>
       </c>
       <c r="P85" s="24">
@@ -6326,64 +6326,64 @@
         </is>
       </c>
     </row>
-    <row r="86" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="86" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
       <c r="A86" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            NODA</t>
+          <t xml:space="preserve">            services</t>
         </is>
       </c>
       <c r="B86" s="4" t="n"/>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>services</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="E86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="F86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="G86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="H86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="I86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="J86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="K86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="L86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="M86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="N86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="O86" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C86)</f>
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C83,'g-expenses-sl'!$F:$F,$C86)</f>
         <v/>
       </c>
       <c r="P86" s="24">
@@ -6399,13 +6399,13 @@
     <row r="87" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A87" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            REGUS</t>
+          <t xml:space="preserve">            NODA</t>
         </is>
       </c>
       <c r="B87" s="4" t="n"/>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="D87" s="5">
@@ -6469,13 +6469,13 @@
     <row r="88" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A88" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            TORRAS</t>
+          <t xml:space="preserve">            REGUS</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="D88" s="5">
@@ -6536,16 +6536,16 @@
         </is>
       </c>
     </row>
-    <row r="89" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="89" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            VITALY</t>
+          <t xml:space="preserve">            TORRAS</t>
         </is>
       </c>
       <c r="B89" s="4" t="n"/>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="D89" s="5">
@@ -6606,141 +6606,141 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="12" customHeight="1">
-      <c r="A90" s="17" t="inlineStr">
+    <row r="90" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+      <c r="A90" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            VITALY</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>VITALY</t>
+        </is>
+      </c>
+      <c r="D90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="E90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="F90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="G90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="H90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="I90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="J90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="K90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="L90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="M90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="N90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="O90" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C90)</f>
+        <v/>
+      </c>
+      <c r="P90" s="24">
+        <f>SUM(D90:O90)</f>
+        <v/>
+      </c>
+      <c r="Q90" s="25" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="12" customHeight="1">
+      <c r="A91" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">        Technology</t>
         </is>
       </c>
-      <c r="B90" s="18" t="n"/>
-      <c r="C90" s="19" t="inlineStr">
+      <c r="B91" s="18" t="n"/>
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D90" s="20">
-        <f>SUM(D91:D106)</f>
-        <v/>
-      </c>
-      <c r="E90" s="20">
-        <f>SUM(E91:E106)</f>
-        <v/>
-      </c>
-      <c r="F90" s="20">
-        <f>SUM(F91:F106)</f>
-        <v/>
-      </c>
-      <c r="G90" s="20">
-        <f>SUM(G91:G106)</f>
-        <v/>
-      </c>
-      <c r="H90" s="20">
-        <f>SUM(H91:H106)</f>
-        <v/>
-      </c>
-      <c r="I90" s="20">
-        <f>SUM(I91:I106)</f>
-        <v/>
-      </c>
-      <c r="J90" s="20">
-        <f>SUM(J91:J106)</f>
-        <v/>
-      </c>
-      <c r="K90" s="20">
-        <f>SUM(K91:K106)</f>
-        <v/>
-      </c>
-      <c r="L90" s="20">
-        <f>SUM(L91:L106)</f>
-        <v/>
-      </c>
-      <c r="M90" s="20">
-        <f>SUM(M91:M106)</f>
-        <v/>
-      </c>
-      <c r="N90" s="20">
-        <f>SUM(N91:N106)</f>
-        <v/>
-      </c>
-      <c r="O90" s="20">
-        <f>SUM(O91:O106)</f>
-        <v/>
-      </c>
-      <c r="P90" s="21">
-        <f>SUM(D90:O90)</f>
-        <v/>
-      </c>
-      <c r="Q90" s="22" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A91" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            ADOBE</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>ADOBE</t>
-        </is>
-      </c>
-      <c r="D91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="E91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="F91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="G91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="H91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="I91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="J91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="K91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="L91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="M91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="N91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="O91" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C91)</f>
-        <v/>
-      </c>
-      <c r="P91" s="24">
+      <c r="D91" s="20">
+        <f>SUM(D92:D107)</f>
+        <v/>
+      </c>
+      <c r="E91" s="20">
+        <f>SUM(E92:E107)</f>
+        <v/>
+      </c>
+      <c r="F91" s="20">
+        <f>SUM(F92:F107)</f>
+        <v/>
+      </c>
+      <c r="G91" s="20">
+        <f>SUM(G92:G107)</f>
+        <v/>
+      </c>
+      <c r="H91" s="20">
+        <f>SUM(H92:H107)</f>
+        <v/>
+      </c>
+      <c r="I91" s="20">
+        <f>SUM(I92:I107)</f>
+        <v/>
+      </c>
+      <c r="J91" s="20">
+        <f>SUM(J92:J107)</f>
+        <v/>
+      </c>
+      <c r="K91" s="20">
+        <f>SUM(K92:K107)</f>
+        <v/>
+      </c>
+      <c r="L91" s="20">
+        <f>SUM(L92:L107)</f>
+        <v/>
+      </c>
+      <c r="M91" s="20">
+        <f>SUM(M92:M107)</f>
+        <v/>
+      </c>
+      <c r="N91" s="20">
+        <f>SUM(N92:N107)</f>
+        <v/>
+      </c>
+      <c r="O91" s="20">
+        <f>SUM(O92:O107)</f>
+        <v/>
+      </c>
+      <c r="P91" s="21">
         <f>SUM(D91:O91)</f>
         <v/>
       </c>
-      <c r="Q91" s="25" t="inlineStr">
+      <c r="Q91" s="22" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -6749,13 +6749,13 @@
     <row r="92" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            CANVA</t>
+          <t xml:space="preserve">            ADOBE</t>
         </is>
       </c>
       <c r="B92" s="4" t="n"/>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D92" s="5">
@@ -6819,13 +6819,13 @@
     <row r="93" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A93" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GODADDY</t>
+          <t xml:space="preserve">            CANVA</t>
         </is>
       </c>
       <c r="B93" s="4" t="n"/>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="D93" s="5">
@@ -6889,13 +6889,13 @@
     <row r="94" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A94" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GOOGLEWORKSPACE</t>
+          <t xml:space="preserve">            GODADDY</t>
         </is>
       </c>
       <c r="B94" s="4" t="n"/>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="D94" s="5">
@@ -6959,13 +6959,13 @@
     <row r="95" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A95" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GORGIAS</t>
+          <t xml:space="preserve">            GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="B95" s="4" t="n"/>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="D95" s="5">
@@ -7029,13 +7029,13 @@
     <row r="96" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            HETZNER</t>
+          <t xml:space="preserve">            GORGIAS</t>
         </is>
       </c>
       <c r="B96" s="4" t="n"/>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="D96" s="5">
@@ -7099,13 +7099,13 @@
     <row r="97" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            KONVOAI</t>
+          <t xml:space="preserve">            HETZNER</t>
         </is>
       </c>
       <c r="B97" s="4" t="n"/>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D97" s="5">
@@ -7169,13 +7169,13 @@
     <row r="98" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            MASMOVIL</t>
+          <t xml:space="preserve">            KONVOAI</t>
         </is>
       </c>
       <c r="B98" s="4" t="n"/>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="D98" s="5">
@@ -7239,13 +7239,13 @@
     <row r="99" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            MICROSOFT</t>
+          <t xml:space="preserve">            MASMOVIL</t>
         </is>
       </c>
       <c r="B99" s="4" t="n"/>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="D99" s="5">
@@ -7309,13 +7309,13 @@
     <row r="100" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A100" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            OPENAI</t>
+          <t xml:space="preserve">            MICROSOFT</t>
         </is>
       </c>
       <c r="B100" s="4" t="n"/>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D100" s="5">
@@ -7379,13 +7379,13 @@
     <row r="101" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A101" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            PRODUCTHERO</t>
+          <t xml:space="preserve">            OPENAI</t>
         </is>
       </c>
       <c r="B101" s="4" t="n"/>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="D101" s="5">
@@ -7449,13 +7449,13 @@
     <row r="102" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A102" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            RAILWAY</t>
+          <t xml:space="preserve">            PRODUCTHERO</t>
         </is>
       </c>
       <c r="B102" s="4" t="n"/>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="D102" s="5">
@@ -7519,13 +7519,13 @@
     <row r="103" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A103" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            REVER</t>
+          <t xml:space="preserve">            RAILWAY</t>
         </is>
       </c>
       <c r="B103" s="4" t="n"/>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -7589,13 +7589,13 @@
     <row r="104" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A104" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            SHOPIFY</t>
+          <t xml:space="preserve">            REVER</t>
         </is>
       </c>
       <c r="B104" s="4" t="n"/>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D104" s="5">
@@ -7659,13 +7659,13 @@
     <row r="105" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A105" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            SYNCWITH</t>
+          <t xml:space="preserve">            SHOPIFY</t>
         </is>
       </c>
       <c r="B105" s="4" t="n"/>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -7726,16 +7726,16 @@
         </is>
       </c>
     </row>
-    <row r="106" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="106" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A106" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            YUMAAI</t>
+          <t xml:space="preserve">            SYNCWITH</t>
         </is>
       </c>
       <c r="B106" s="4" t="n"/>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="D106" s="5">
@@ -7796,71 +7796,71 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="12" customHeight="1">
-      <c r="A107" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="B107" s="18" t="n"/>
-      <c r="C107" s="19" t="inlineStr">
-        <is>
-          <t>Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="D107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="E107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="F107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="G107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="H107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="I107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="J107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="K107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="L107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="M107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="N107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="O107" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="P107" s="21">
+    <row r="107" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            YUMAAI</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="D107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="E107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="F107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="G107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="H107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="I107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="J107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="K107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="L107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="M107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="N107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="O107" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C107)</f>
+        <v/>
+      </c>
+      <c r="P107" s="24">
         <f>SUM(D107:O107)</f>
         <v/>
       </c>
-      <c r="Q107" s="22" t="inlineStr">
+      <c r="Q107" s="25" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -7869,182 +7869,252 @@
     <row r="108" ht="12" customHeight="1">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Currency Adjustment</t>
-        </is>
-      </c>
-      <c r="B108" s="19" t="inlineStr">
-        <is>
-          <t>Currency Adjustment</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="20" t="n">
-        <v>-132.9</v>
-      </c>
-      <c r="E108" s="20" t="n">
-        <v>-277.52</v>
-      </c>
-      <c r="F108" s="20" t="n"/>
-      <c r="G108" s="20" t="n"/>
-      <c r="H108" s="20" t="n"/>
-      <c r="I108" s="20" t="n"/>
-      <c r="J108" s="20" t="n"/>
-      <c r="K108" s="20" t="n"/>
-      <c r="L108" s="20" t="n"/>
-      <c r="M108" s="20" t="n"/>
-      <c r="N108" s="20" t="n"/>
-      <c r="O108" s="20" t="n"/>
+          <t xml:space="preserve">        Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="n"/>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="D108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O108" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
       <c r="P108" s="21">
         <f>SUM(D108:O108)</f>
         <v/>
       </c>
-      <c r="Q108" s="27" t="n"/>
+      <c r="Q108" s="22" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="12" customHeight="1">
-      <c r="A109" s="4" t="n"/>
-      <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="5" t="n"/>
-      <c r="F109" s="5" t="n"/>
-      <c r="G109" s="5" t="n"/>
-      <c r="H109" s="5" t="n"/>
-      <c r="I109" s="5" t="n"/>
-      <c r="J109" s="5" t="n"/>
-      <c r="K109" s="5" t="n"/>
-      <c r="L109" s="5" t="n"/>
-      <c r="M109" s="5" t="n"/>
-      <c r="N109" s="5" t="n"/>
-      <c r="O109" s="5" t="n"/>
-      <c r="P109" s="24">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="20" t="n">
+        <v>-132.9</v>
+      </c>
+      <c r="E109" s="20" t="n">
+        <v>-277.52</v>
+      </c>
+      <c r="F109" s="20" t="n"/>
+      <c r="G109" s="20" t="n"/>
+      <c r="H109" s="20" t="n"/>
+      <c r="I109" s="20" t="n"/>
+      <c r="J109" s="20" t="n"/>
+      <c r="K109" s="20" t="n"/>
+      <c r="L109" s="20" t="n"/>
+      <c r="M109" s="20" t="n"/>
+      <c r="N109" s="20" t="n"/>
+      <c r="O109" s="20" t="n"/>
+      <c r="P109" s="21">
         <f>SUM(D109:O109)</f>
         <v/>
       </c>
-      <c r="Q109" s="5" t="n"/>
+      <c r="Q109" s="27" t="n"/>
     </row>
     <row r="110" ht="12" customHeight="1">
-      <c r="A110" s="33" t="inlineStr">
+      <c r="A110" s="4" t="n"/>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="5" t="n"/>
+      <c r="F110" s="5" t="n"/>
+      <c r="G110" s="5" t="n"/>
+      <c r="H110" s="5" t="n"/>
+      <c r="I110" s="5" t="n"/>
+      <c r="J110" s="5" t="n"/>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="24">
+        <f>SUM(D110:O110)</f>
+        <v/>
+      </c>
+      <c r="Q110" s="5" t="n"/>
+    </row>
+    <row r="111" ht="12" customHeight="1">
+      <c r="A111" s="33" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B110" s="34" t="n"/>
-      <c r="C110" s="34" t="n"/>
-      <c r="D110" s="35">
-        <f>D4-D33-D64-D108</f>
-        <v/>
-      </c>
-      <c r="E110" s="35">
-        <f>E4-E33-E64-E108</f>
-        <v/>
-      </c>
-      <c r="F110" s="35">
-        <f>F4-F33-F64-F108</f>
-        <v/>
-      </c>
-      <c r="G110" s="35">
-        <f>G4-G33-G64-G108</f>
-        <v/>
-      </c>
-      <c r="H110" s="35">
-        <f>H4-H33-H64-H108</f>
-        <v/>
-      </c>
-      <c r="I110" s="35">
-        <f>I4-I33-I64-I108</f>
-        <v/>
-      </c>
-      <c r="J110" s="35">
-        <f>J4-J33-J64-J108</f>
-        <v/>
-      </c>
-      <c r="K110" s="35">
-        <f>K4-K33-K64-K108</f>
-        <v/>
-      </c>
-      <c r="L110" s="35">
-        <f>L4-L33-L64-L108</f>
-        <v/>
-      </c>
-      <c r="M110" s="35">
-        <f>M4-M33-M64-M108</f>
-        <v/>
-      </c>
-      <c r="N110" s="35">
-        <f>N4-N33-N64-N108</f>
-        <v/>
-      </c>
-      <c r="O110" s="35">
-        <f>O4-O33-O64-O108</f>
-        <v/>
-      </c>
-      <c r="P110" s="9">
-        <f>SUM(D110:O110)</f>
-        <v/>
-      </c>
-      <c r="Q110" s="36" t="n"/>
-    </row>
-    <row r="111" ht="12" customHeight="1">
-      <c r="A111" s="37" t="inlineStr">
+      <c r="B111" s="34" t="n"/>
+      <c r="C111" s="34" t="n"/>
+      <c r="D111" s="35">
+        <f>D4-D33-D64-D109</f>
+        <v/>
+      </c>
+      <c r="E111" s="35">
+        <f>E4-E33-E64-E109</f>
+        <v/>
+      </c>
+      <c r="F111" s="35">
+        <f>F4-F33-F64-F109</f>
+        <v/>
+      </c>
+      <c r="G111" s="35">
+        <f>G4-G33-G64-G109</f>
+        <v/>
+      </c>
+      <c r="H111" s="35">
+        <f>H4-H33-H64-H109</f>
+        <v/>
+      </c>
+      <c r="I111" s="35">
+        <f>I4-I33-I64-I109</f>
+        <v/>
+      </c>
+      <c r="J111" s="35">
+        <f>J4-J33-J64-J109</f>
+        <v/>
+      </c>
+      <c r="K111" s="35">
+        <f>K4-K33-K64-K109</f>
+        <v/>
+      </c>
+      <c r="L111" s="35">
+        <f>L4-L33-L64-L109</f>
+        <v/>
+      </c>
+      <c r="M111" s="35">
+        <f>M4-M33-M64-M109</f>
+        <v/>
+      </c>
+      <c r="N111" s="35">
+        <f>N4-N33-N64-N109</f>
+        <v/>
+      </c>
+      <c r="O111" s="35">
+        <f>O4-O33-O64-O109</f>
+        <v/>
+      </c>
+      <c r="P111" s="9">
+        <f>SUM(D111:O111)</f>
+        <v/>
+      </c>
+      <c r="Q111" s="36" t="n"/>
+    </row>
+    <row r="112" ht="12" customHeight="1">
+      <c r="A112" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">        % profit / product sales</t>
         </is>
       </c>
-      <c r="B111" s="38" t="n"/>
-      <c r="C111" s="38" t="n"/>
-      <c r="D111" s="39">
-        <f>IFERROR(D110/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E111" s="39">
-        <f>IFERROR(E110/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F111" s="39">
-        <f>IFERROR(F110/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G111" s="39">
-        <f>IFERROR(G110/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H111" s="39">
-        <f>IFERROR(H110/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I111" s="39">
-        <f>IFERROR(I110/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J111" s="39">
-        <f>IFERROR(J110/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K111" s="39">
-        <f>IFERROR(K110/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L111" s="39">
-        <f>IFERROR(L110/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M111" s="39">
-        <f>IFERROR(M110/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N111" s="39">
-        <f>IFERROR(N110/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O111" s="39">
-        <f>IFERROR(O110/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P111" s="40">
-        <f>IFERROR(P110/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q111" s="31" t="n"/>
+      <c r="B112" s="38" t="n"/>
+      <c r="C112" s="38" t="n"/>
+      <c r="D112" s="39">
+        <f>IFERROR(D111/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E112" s="39">
+        <f>IFERROR(E111/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F112" s="39">
+        <f>IFERROR(F111/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G112" s="39">
+        <f>IFERROR(G111/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H112" s="39">
+        <f>IFERROR(H111/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I112" s="39">
+        <f>IFERROR(I111/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J112" s="39">
+        <f>IFERROR(J111/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K112" s="39">
+        <f>IFERROR(K111/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L112" s="39">
+        <f>IFERROR(L111/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M112" s="39">
+        <f>IFERROR(M111/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N112" s="39">
+        <f>IFERROR(N111/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O112" s="39">
+        <f>IFERROR(O111/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P112" s="40">
+        <f>IFERROR(P111/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q112" s="31" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8134,6 +8204,7 @@
     <hyperlink ref="Q105" location="'g-expenses-sl'!A1" display="-&gt;"/>
     <hyperlink ref="Q106" location="'g-expenses-sl'!A1" display="-&gt;"/>
     <hyperlink ref="Q107" location="'g-expenses-sl'!A1" display="-&gt;"/>
+    <hyperlink ref="Q108" location="'g-expenses-sl'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9139,7 +9210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9467,17 +9538,17 @@
     <row r="14" ht="12" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BBVACNC</t>
+          <t>ADEPLUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
+          <t>ADEPLUS CONSULTORES, S.L.U.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>Adeplus</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9485,22 +9556,26 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data protection services</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="12" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>BBVACNC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9513,17 +9588,17 @@
     <row r="16" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONTASIMPLE</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CEGID SMB, S.A.U</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contasimple</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9531,26 +9606,22 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Accounting software subscription</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17" ht="12" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>Contasimple</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9560,24 +9631,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bidirectional HANNUN relationship; incoming expense invoices and outgoing customer invoices</t>
+          <t>Accounting software subscription</t>
         </is>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NODA Asesores</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -9585,22 +9656,26 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bidirectional HANNUN relationship; incoming expense invoices and outgoing customer invoices</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="12" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>regus</t>
+          <t>NODA Asesores</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -9613,17 +9688,17 @@
     <row r="20" ht="12" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>regus</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9636,17 +9711,17 @@
     <row r="21" ht="12" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -9654,49 +9729,49 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Annual prevention and occupational health service</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22" ht="12" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>expenses/opex/marketing</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>expenses/opex/administration</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Annual prevention and occupational health service</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="12" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>METAADS</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>METAADS</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9709,67 +9784,67 @@
     <row r="24" ht="12" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DOSCONSULTING</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DOSCONSULTING</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nóminas</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>expenses/opex/staff</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Monthly payroll management for SL</t>
-        </is>
-      </c>
+          <t>expenses/opex/marketing</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>DOSCONSULTING</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>DOSCONSULTING</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>Nóminas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>expenses/opex/technology</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>expenses/opex/staff</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Monthly payroll management for SL</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>canva</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -9782,17 +9857,17 @@
     <row r="27" ht="12" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>godaddy</t>
+          <t>canva</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -9805,17 +9880,17 @@
     <row r="28" ht="12" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>godaddy</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -9828,17 +9903,17 @@
     <row r="29" ht="12" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gorgias</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -9851,17 +9926,17 @@
     <row r="30" ht="12" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>Gorgias</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9874,17 +9949,17 @@
     <row r="31" ht="12" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>konvo</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -9897,17 +9972,17 @@
     <row r="32" ht="12" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>mas movil</t>
+          <t>konvo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9920,17 +9995,17 @@
     <row r="33" ht="12" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>mas movil</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9943,17 +10018,17 @@
     <row r="34" ht="12" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9961,26 +10036,22 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Groups ChatGPT and API</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35" ht="12" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ProductHERO</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -9988,22 +10059,26 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Groups ChatGPT and API</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="12" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>ProductHERO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -10016,17 +10091,17 @@
     <row r="37" ht="12" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -10039,17 +10114,17 @@
     <row r="38" ht="12" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -10062,17 +10137,17 @@
     <row r="39" ht="12" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SyncWith</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -10080,26 +10155,22 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Monthly subscription invoiced one month in arrears</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40" ht="12" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YUMA</t>
+          <t>SyncWith</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -10107,76 +10178,76 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Monthly subscription invoiced one month in arrears</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="12" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LIVITUM</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LIVITUM</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>709. Rappels</t>
+          <t>YUMA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>income/other_income/rappels</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Rappel issued to Livitum</t>
-        </is>
-      </c>
+          <t>expenses/opex/technology</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42" ht="12" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>LIVITUM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>LIVITUM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>709. Rappels</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>income/sales/marketplaces</t>
+          <t>income/other_income/rappels</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Outgoing partner invoice</t>
+          <t>Rappel issued to Livitum</t>
         </is>
       </c>
     </row>
     <row r="43" ht="12" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>CHOOSE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>CHOOSE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>CHOOSE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10193,25 +10264,52 @@
     <row r="44" ht="12" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>income/sales/marketplaces</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Outgoing partner invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="12" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>income/shared-services</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Outgoing CNC rental invoice</t>
         </is>
@@ -10412,7 +10510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q99"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13496,11 +13594,11 @@
     <row r="70" ht="12" customHeight="1">
       <c r="C70" t="inlineStr">
         <is>
-          <t>BBVACNC</t>
+          <t>ADEPLUS</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -13536,13 +13634,13 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1">
       <c r="C71" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>BBVACNC</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -13552,10 +13650,10 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -13582,26 +13680,26 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1">
       <c r="C72" t="inlineStr">
         <is>
-          <t>CONTASIMPLE</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="56" t="n">
-        <v>0</v>
+      <c r="G72" t="n">
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -13628,25 +13726,25 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1">
       <c r="C73" t="inlineStr">
         <is>
-          <t>HANNUN</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
-      </c>
-      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
@@ -13674,25 +13772,25 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1">
       <c r="C74" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>HANNUN</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
@@ -13720,20 +13818,20 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" ht="12" customHeight="1">
       <c r="C75" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
@@ -13766,13 +13864,13 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1">
       <c r="C76" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>office</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -13818,19 +13916,19 @@
     <row r="77" ht="12" customHeight="1">
       <c r="C77" t="inlineStr">
         <is>
-          <t>NODA</t>
+          <t>services</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
@@ -13858,17 +13956,17 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" ht="12" customHeight="1">
       <c r="C78" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -13904,26 +14002,26 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" ht="12" customHeight="1">
       <c r="C79" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -13950,154 +14048,154 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" ht="12" customHeight="1">
       <c r="C80" t="inlineStr">
         <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" ht="12" customHeight="1">
+      <c r="C81" t="inlineStr">
+        <is>
           <t>VITALY</t>
         </is>
       </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" ht="12" customHeight="1">
-      <c r="A81" s="54" t="n"/>
-      <c r="B81" s="54" t="n"/>
-      <c r="C81" s="55" t="inlineStr">
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="12" customHeight="1">
+      <c r="A82" s="54" t="n"/>
+      <c r="B82" s="54" t="n"/>
+      <c r="C82" s="55" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D81" s="54" t="n">
+      <c r="D82" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="E81" s="54" t="n">
+      <c r="E82" s="54" t="n">
         <v>21</v>
       </c>
-      <c r="F81" s="54" t="n">
+      <c r="F82" s="54" t="n">
         <v>23</v>
       </c>
-      <c r="G81" s="54" t="n">
+      <c r="G82" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="H81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="54" t="n">
+      <c r="H82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="54" t="n">
         <v>66</v>
       </c>
-      <c r="Q81" s="54" t="n"/>
-    </row>
-    <row r="82" ht="12" customHeight="1">
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>ADOBE</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>3</v>
-      </c>
+      <c r="Q82" s="54" t="n"/>
     </row>
     <row r="83" ht="12" customHeight="1">
       <c r="C83" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -14143,17 +14241,17 @@
     <row r="84" ht="12" customHeight="1">
       <c r="C84" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="56" t="n">
         <v>0</v>
@@ -14183,23 +14281,23 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" ht="12" customHeight="1">
       <c r="C85" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G85" s="56" t="n">
         <v>0</v>
@@ -14229,13 +14327,13 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" ht="12" customHeight="1">
       <c r="C86" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -14281,7 +14379,7 @@
     <row r="87" ht="12" customHeight="1">
       <c r="C87" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -14291,9 +14389,9 @@
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="56" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
@@ -14321,69 +14419,69 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" ht="12" customHeight="1">
       <c r="C88" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
         <v>2</v>
-      </c>
-      <c r="E88" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" t="n">
-        <v>3</v>
-      </c>
-      <c r="G88" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="89" ht="12" customHeight="1">
       <c r="C89" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G89" s="56" t="n">
         <v>0</v>
@@ -14413,23 +14511,23 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" ht="12" customHeight="1">
       <c r="C90" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G90" s="56" t="n">
         <v>0</v>
@@ -14459,66 +14557,66 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" ht="12" customHeight="1">
       <c r="C91" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>2</v>
       </c>
       <c r="E91" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
         <v>6</v>
-      </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="92" ht="12" customHeight="1">
       <c r="C92" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -14551,13 +14649,13 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" ht="12" customHeight="1">
       <c r="C93" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -14569,8 +14667,8 @@
       <c r="F93" t="n">
         <v>1</v>
       </c>
-      <c r="G93" t="n">
-        <v>1</v>
+      <c r="G93" s="56" t="n">
+        <v>0</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -14597,25 +14695,25 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" ht="12" customHeight="1">
       <c r="C94" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
-      </c>
-      <c r="G94" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
         <v>1</v>
       </c>
       <c r="H94" t="n">
@@ -14643,26 +14741,26 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" ht="12" customHeight="1">
       <c r="C95" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G95" s="56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -14689,23 +14787,23 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" ht="12" customHeight="1">
       <c r="C96" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G96" s="56" t="n">
         <v>0</v>
@@ -14741,17 +14839,17 @@
     <row r="97" ht="12" customHeight="1">
       <c r="C97" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G97" s="56" t="n">
         <v>0</v>
@@ -14785,62 +14883,59 @@
       </c>
     </row>
     <row r="98" ht="12" customHeight="1">
-      <c r="A98" s="54" t="n"/>
-      <c r="B98" s="54" t="n"/>
-      <c r="C98" s="55" t="inlineStr">
-        <is>
-          <t>Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="D98" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q98" s="54" t="n"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="99" ht="12" customHeight="1">
       <c r="A99" s="54" t="n"/>
-      <c r="B99" s="55" t="inlineStr">
-        <is>
-          <t>Currency Adjustment</t>
-        </is>
-      </c>
-      <c r="C99" s="54" t="n"/>
+      <c r="B99" s="54" t="n"/>
+      <c r="C99" s="55" t="inlineStr">
+        <is>
+          <t>Uncategorized Expenses</t>
+        </is>
+      </c>
       <c r="D99" s="54" t="n">
         <v>1</v>
       </c>
@@ -14881,6 +14976,55 @@
         <v>2</v>
       </c>
       <c r="Q99" s="54" t="n"/>
+    </row>
+    <row r="100" ht="12" customHeight="1">
+      <c r="A100" s="54" t="n"/>
+      <c r="B100" s="55" t="inlineStr">
+        <is>
+          <t>Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="C100" s="54" t="n"/>
+      <c r="D100" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q100" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15273,51 +15417,51 @@
         </is>
       </c>
       <c r="D8" s="47">
-        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="E8" s="47">
-        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="F8" s="47">
-        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="G8" s="47">
-        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="H8" s="47">
-        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="I8" s="47">
-        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="J8" s="47">
-        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="K8" s="47">
-        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="L8" s="47">
-        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="M8" s="47">
-        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="N8" s="47">
-        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="O8" s="47">
-        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O90)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O91)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="P8" s="47">
@@ -15676,51 +15820,51 @@
         </is>
       </c>
       <c r="D16" s="47">
-        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!D78+'P&amp;G-SL'!D91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="E16" s="47">
-        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!E78+'P&amp;G-SL'!E91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="F16" s="47">
-        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!F78+'P&amp;G-SL'!F91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="G16" s="47">
-        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!G78+'P&amp;G-SL'!G91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="H16" s="47">
-        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!H78+'P&amp;G-SL'!H91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="I16" s="47">
-        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!I78+'P&amp;G-SL'!I91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="J16" s="47">
-        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!J78+'P&amp;G-SL'!J91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="K16" s="47">
-        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!K78+'P&amp;G-SL'!K91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="L16" s="47">
-        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!L78+'P&amp;G-SL'!L91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="M16" s="47">
-        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!M78+'P&amp;G-SL'!M91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="N16" s="47">
-        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!N78+'P&amp;G-SL'!N91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="O16" s="47">
-        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O90)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!O78+'P&amp;G-SL'!O91)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="P16" s="47">
@@ -15989,7 +16133,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-04-10T09:47:54Z</t>
+          <t>2026-04-10T10:53:37Z</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17691,7 @@
         </is>
       </c>
       <c r="E32" s="47" t="n">
-        <v>6557.08</v>
+        <v>6552.92</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -17563,7 +17707,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="47" t="n">
-        <v>6557.08</v>
+        <v>6552.92</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -17595,7 +17739,7 @@
         </is>
       </c>
       <c r="E33" s="47" t="n">
-        <v>31818.42</v>
+        <v>32201.17</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -17611,7 +17755,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="47" t="n">
-        <v>31818.42</v>
+        <v>32201.17</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -17643,7 +17787,7 @@
         </is>
       </c>
       <c r="E34" s="47" t="n">
-        <v>10154.56</v>
+        <v>10277.8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -17659,7 +17803,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="47" t="n">
-        <v>10154.56</v>
+        <v>10277.8</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -19433,7 +19577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N180"/>
+  <dimension ref="A1:N181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23049,17 +23193,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>ADEPLUS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" s="47" t="n">
-        <v>33.49</v>
+        <v>309.02</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -23075,7 +23219,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="47" t="n">
-        <v>33.49</v>
+        <v>309.02</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -23084,12 +23228,12 @@
       </c>
       <c r="M59" s="49" t="inlineStr">
         <is>
-          <t>IEE2026003947036</t>
+          <t>IFC2602-00689</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CkpniiuuecmyeP38MmkWhzUPj8iF7tyN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Q01w19CaQwCYwshExpbnKigbbpkdYcRF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23106,22 +23250,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>APPHOTOCAN</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" s="47" t="n">
-        <v>59.84</v>
+        <v>33.49</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -23137,7 +23281,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="47" t="n">
-        <v>59.84</v>
+        <v>33.49</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -23146,12 +23290,12 @@
       </c>
       <c r="M60" s="49" t="inlineStr">
         <is>
-          <t>26-1-377</t>
+          <t>IEE2026003947036</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U-mcMTxSs8WKlovQ9_HAwLEU39hou9sQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CkpniiuuecmyeP38MmkWhzUPj8iF7tyN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23178,12 +23322,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>APPHOTOES</t>
+          <t>APPHOTOCAN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" s="47" t="n">
-        <v>761.54</v>
+        <v>59.84</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -23199,7 +23343,7 @@
         <v>1</v>
       </c>
       <c r="K61" s="47" t="n">
-        <v>761.54</v>
+        <v>59.84</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -23208,12 +23352,12 @@
       </c>
       <c r="M61" s="49" t="inlineStr">
         <is>
-          <t>1-1413</t>
+          <t>26-1-377</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1i1KIDpqSuLOk5KfVZf0GwoQN3ddbzHi4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1U-mcMTxSs8WKlovQ9_HAwLEU39hou9sQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23245,7 +23389,7 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" s="47" t="n">
-        <v>4679.01</v>
+        <v>761.54</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -23261,7 +23405,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="47" t="n">
-        <v>4679.01</v>
+        <v>761.54</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -23270,12 +23414,12 @@
       </c>
       <c r="M62" s="49" t="inlineStr">
         <is>
-          <t>1-1578</t>
+          <t>1-1413</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aVT0Kp1FXhiwKuldPvpR5jmS_HrroAcz/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1i1KIDpqSuLOk5KfVZf0GwoQN3ddbzHi4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23307,7 +23451,7 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" s="47" t="n">
-        <v>4387.66</v>
+        <v>4679.01</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -23323,7 +23467,7 @@
         <v>1</v>
       </c>
       <c r="K63" s="47" t="n">
-        <v>4387.66</v>
+        <v>4679.01</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -23332,12 +23476,12 @@
       </c>
       <c r="M63" s="49" t="inlineStr">
         <is>
-          <t>1-1960</t>
+          <t>1-1578</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1c3rAE8MZ72DBnTA6LZZqeHMMgZkJtDwC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aVT0Kp1FXhiwKuldPvpR5jmS_HrroAcz/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23369,7 +23513,7 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" s="47" t="n">
-        <v>1523.96</v>
+        <v>4387.66</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -23385,7 +23529,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="47" t="n">
-        <v>1523.96</v>
+        <v>4387.66</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -23394,12 +23538,12 @@
       </c>
       <c r="M64" s="49" t="inlineStr">
         <is>
-          <t>1-2275</t>
+          <t>1-1960</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hZiPKVEudy0sryGytMftZTSO75OBheV_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1c3rAE8MZ72DBnTA6LZZqeHMMgZkJtDwC/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23431,7 +23575,7 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" s="47" t="n">
-        <v>4898.31</v>
+        <v>1523.96</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -23447,7 +23591,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="47" t="n">
-        <v>4898.31</v>
+        <v>1523.96</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -23456,12 +23600,12 @@
       </c>
       <c r="M65" s="49" t="inlineStr">
         <is>
-          <t>1-2355</t>
+          <t>1-2275</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1aXemXVZg0sBlWBgHV0_QAg0jVjv1bksN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hZiPKVEudy0sryGytMftZTSO75OBheV_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23493,7 +23637,7 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" s="47" t="n">
-        <v>975.1900000000001</v>
+        <v>4898.31</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -23509,7 +23653,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="47" t="n">
-        <v>975.1900000000001</v>
+        <v>4898.31</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -23518,12 +23662,12 @@
       </c>
       <c r="M66" s="49" t="inlineStr">
         <is>
-          <t>1-2471</t>
+          <t>1-2355</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vWJy2P4bu0ZZHbeutrY9ydZYIScfPKex/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1aXemXVZg0sBlWBgHV0_QAg0jVjv1bksN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23555,7 +23699,7 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" s="47" t="n">
-        <v>5761.46</v>
+        <v>975.1900000000001</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -23571,7 +23715,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="47" t="n">
-        <v>5761.46</v>
+        <v>975.1900000000001</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -23580,12 +23724,12 @@
       </c>
       <c r="M67" s="49" t="inlineStr">
         <is>
-          <t>1-2675</t>
+          <t>1-2471</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OPWZpghAzzfVFLFx4iBRHO4-0daxuz20/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vWJy2P4bu0ZZHbeutrY9ydZYIScfPKex/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23602,22 +23746,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BBVACNC</t>
+          <t>APPHOTOES</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" s="47" t="n">
-        <v>1644.62</v>
+        <v>5761.46</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -23633,15 +23777,23 @@
         <v>1</v>
       </c>
       <c r="K68" s="47" t="n">
-        <v>1644.62</v>
+        <v>5761.46</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="M68" s="49" t="inlineStr">
+        <is>
+          <t>1-2675</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1OPWZpghAzzfVFLFx4iBRHO4-0daxuz20/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="12" customHeight="1">
       <c r="A69" t="inlineStr">
@@ -23661,17 +23813,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>BBVACNC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" s="47" t="n">
-        <v>9.91</v>
+        <v>1644.62</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -23687,23 +23839,15 @@
         <v>1</v>
       </c>
       <c r="K69" s="47" t="n">
-        <v>9.91</v>
+        <v>1644.62</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>documents</t>
         </is>
       </c>
-      <c r="M69" s="49" t="inlineStr">
-        <is>
-          <t>04796-33900634</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1dEu5a12XOSJxoPOd8AIxLplDtcRjC5z9/view?usp=drivesdk</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70" ht="12" customHeight="1">
       <c r="A70" t="inlineStr">
@@ -23723,17 +23867,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" s="47" t="n">
-        <v>808.08</v>
+        <v>9.91</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -23749,7 +23893,7 @@
         <v>1</v>
       </c>
       <c r="K70" s="47" t="n">
-        <v>808.08</v>
+        <v>9.91</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -23758,12 +23902,12 @@
       </c>
       <c r="M70" s="49" t="inlineStr">
         <is>
-          <t>F00299/26</t>
+          <t>04796-33900634</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1wkA555zHmi_P1F3K0yzi2R1ybg40M_IH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dEu5a12XOSJxoPOd8AIxLplDtcRjC5z9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23780,22 +23924,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CORREOS</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" s="47" t="n">
-        <v>96.77</v>
+        <v>808.08</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -23811,7 +23955,7 @@
         <v>1</v>
       </c>
       <c r="K71" s="47" t="n">
-        <v>96.77</v>
+        <v>808.08</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -23820,12 +23964,12 @@
       </c>
       <c r="M71" s="49" t="inlineStr">
         <is>
-          <t>4004608215</t>
+          <t>F00299/26</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Bu6kn877nOS0BSzL7ECg9Z62seXoHaCe/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1wkA555zHmi_P1F3K0yzi2R1ybg40M_IH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23852,12 +23996,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CORREOSCAN</t>
+          <t>CORREOS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" s="47" t="n">
-        <v>16.45</v>
+        <v>96.77</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -23873,7 +24017,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="47" t="n">
-        <v>16.45</v>
+        <v>96.77</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -23882,12 +24026,12 @@
       </c>
       <c r="M72" s="49" t="inlineStr">
         <is>
-          <t>4004608216</t>
+          <t>4004608215</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1eD4nKiQgwGYnGZ5fv7hh4V3unZ6MIKqH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Bu6kn877nOS0BSzL7ECg9Z62seXoHaCe/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23909,17 +24053,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>CORREOSCAN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" s="47" t="n">
-        <v>3443.83</v>
+        <v>16.45</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -23935,7 +24079,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="47" t="n">
-        <v>3443.83</v>
+        <v>16.45</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -23944,12 +24088,12 @@
       </c>
       <c r="M73" s="49" t="inlineStr">
         <is>
-          <t>26-0281</t>
+          <t>4004608216</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1H2ikEjq_KT22RCYpKdLTU6AyxE-eiIW-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1eD4nKiQgwGYnGZ5fv7hh4V3unZ6MIKqH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -23981,7 +24125,7 @@
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" s="47" t="n">
-        <v>3438.99</v>
+        <v>3443.83</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -23997,7 +24141,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="47" t="n">
-        <v>3438.99</v>
+        <v>3443.83</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -24006,12 +24150,12 @@
       </c>
       <c r="M74" s="49" t="inlineStr">
         <is>
-          <t>26-0364</t>
+          <t>26-0281</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YrSUC_u5-Y5IQ7Aslne-0xU3mQfg3jDp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1H2ikEjq_KT22RCYpKdLTU6AyxE-eiIW-/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24187,7 @@
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" s="47" t="n">
-        <v>42.5</v>
+        <v>3438.99</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -24059,7 +24203,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="47" t="n">
-        <v>42.5</v>
+        <v>3438.99</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -24068,12 +24212,12 @@
       </c>
       <c r="M75" s="49" t="inlineStr">
         <is>
-          <t>26-0365</t>
+          <t>26-0364</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/109-KgtoaX4vV_BNFkqOESzhRasVQ1S_Q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YrSUC_u5-Y5IQ7Aslne-0xU3mQfg3jDp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24095,17 +24239,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" s="47" t="n">
-        <v>15947.02</v>
+        <v>42.5</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -24121,7 +24265,7 @@
         <v>1</v>
       </c>
       <c r="K76" s="47" t="n">
-        <v>15947.02</v>
+        <v>42.5</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -24130,12 +24274,12 @@
       </c>
       <c r="M76" s="49" t="inlineStr">
         <is>
-          <t>20260082</t>
+          <t>26-0365</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1KY46ho8xsJpWU6Q3w32ZWRQ8btywV8Ax/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/109-KgtoaX4vV_BNFkqOESzhRasVQ1S_Q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24152,26 +24296,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>eu</t>
-        </is>
-      </c>
+          <t>GLS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" s="47" t="n">
-        <v>19199.14</v>
+        <v>15947.02</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -24187,7 +24327,7 @@
         <v>1</v>
       </c>
       <c r="K77" s="47" t="n">
-        <v>19199.14</v>
+        <v>15947.02</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -24196,12 +24336,12 @@
       </c>
       <c r="M77" s="49" t="inlineStr">
         <is>
-          <t>5509802536</t>
+          <t>20260082</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/192ghVBMKOyFtFrKk5lPoccixcsZlK4GH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KY46ho8xsJpWU6Q3w32ZWRQ8btywV8Ax/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24233,11 +24373,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="G78" s="47" t="n">
-        <v>5006.17</v>
+        <v>19199.14</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -24253,7 +24393,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="47" t="n">
-        <v>5006.17</v>
+        <v>19199.14</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -24299,11 +24439,11 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G79" s="47" t="n">
-        <v>3345.8</v>
+        <v>5006.17</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -24319,7 +24459,7 @@
         <v>1</v>
       </c>
       <c r="K79" s="47" t="n">
-        <v>3345.8</v>
+        <v>5006.17</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -24355,17 +24495,21 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G80" s="47" t="n">
-        <v>201.91</v>
+        <v>3345.8</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -24381,7 +24525,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="47" t="n">
-        <v>201.91</v>
+        <v>3345.8</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -24390,12 +24534,12 @@
       </c>
       <c r="M80" s="49" t="inlineStr">
         <is>
-          <t>5505030303</t>
+          <t>5509802536</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_odcqxdXxEYZNzgQx5UzslhIG3hh5krH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/192ghVBMKOyFtFrKk5lPoccixcsZlK4GH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24422,16 +24566,16 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" s="47" t="n">
-        <v>120</v>
+        <v>201.91</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -24440,10 +24584,10 @@
         </is>
       </c>
       <c r="J81" s="48" t="n">
-        <v>0.84709869</v>
+        <v>1</v>
       </c>
       <c r="K81" s="47" t="n">
-        <v>101.65</v>
+        <v>201.91</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -24452,19 +24596,19 @@
       </c>
       <c r="M81" s="49" t="inlineStr">
         <is>
-          <t>INC-02-2026-50341</t>
+          <t>5505030303</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tAciOjLJ3-E_udDrY3cL0A7b-CfOvIlm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_odcqxdXxEYZNzgQx5UzslhIG3hh5krH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="82" ht="12" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -24479,25 +24623,21 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HANNUN</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>office</t>
-        </is>
-      </c>
+          <t>GORGIAS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" s="47" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -24506,10 +24646,10 @@
         </is>
       </c>
       <c r="J82" s="48" t="n">
-        <v>1</v>
+        <v>0.84709869</v>
       </c>
       <c r="K82" s="47" t="n">
-        <v>175</v>
+        <v>101.65</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -24518,19 +24658,19 @@
       </c>
       <c r="M82" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-010327</t>
+          <t>INC-02-2026-50341</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1E8JfN7YXvjRIfPjaLKj_8zJSQJ-990YT/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tAciOjLJ3-E_udDrY3cL0A7b-CfOvIlm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="83" ht="12" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -24584,19 +24724,19 @@
       </c>
       <c r="M83" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-010329</t>
+          <t>VTA/26-010327</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1r2Hw0N7VZ6vvloF4IqY4SxfuvX_2VozE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1E8JfN7YXvjRIfPjaLKj_8zJSQJ-990YT/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="84" ht="12" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -24621,11 +24761,11 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>office</t>
         </is>
       </c>
       <c r="G84" s="47" t="n">
-        <v>1504.92</v>
+        <v>175</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -24641,7 +24781,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="47" t="n">
-        <v>1504.92</v>
+        <v>175</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -24650,19 +24790,19 @@
       </c>
       <c r="M84" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-010328</t>
+          <t>VTA/26-010329</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PRJ__aaxThVGTbIcvHAJI7pgUFchpvsa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r2Hw0N7VZ6vvloF4IqY4SxfuvX_2VozE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="85" ht="12" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -24716,12 +24856,12 @@
       </c>
       <c r="M85" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-010330</t>
+          <t>VTA/26-010328</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HgIvIqgrCSyQY0-INtfhp-GPqb5Et1eA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PRJ__aaxThVGTbIcvHAJI7pgUFchpvsa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24743,17 +24883,21 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HETZNER</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
       <c r="G86" s="47" t="n">
-        <v>10.9</v>
+        <v>1504.92</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -24769,7 +24913,7 @@
         <v>1</v>
       </c>
       <c r="K86" s="47" t="n">
-        <v>10.9</v>
+        <v>1504.92</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -24778,12 +24922,12 @@
       </c>
       <c r="M86" s="49" t="inlineStr">
         <is>
-          <t>086000751422</t>
+          <t>VTA/26-010330</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bMdMTYSXLytnvUKxINvo3C-fdr43SmgJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1HgIvIqgrCSyQY0-INtfhp-GPqb5Et1eA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24810,12 +24954,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" s="47" t="n">
-        <v>136.96</v>
+        <v>10.9</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -24831,7 +24975,7 @@
         <v>1</v>
       </c>
       <c r="K87" s="47" t="n">
-        <v>136.96</v>
+        <v>10.9</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -24840,12 +24984,12 @@
       </c>
       <c r="M87" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7132</t>
+          <t>086000751422</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1n2bq_tMI3rNE2XsFpxvWnwo1ZZV6_K21/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bMdMTYSXLytnvUKxINvo3C-fdr43SmgJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24877,7 +25021,7 @@
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" s="47" t="n">
-        <v>339</v>
+        <v>136.96</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -24893,7 +25037,7 @@
         <v>1</v>
       </c>
       <c r="K88" s="47" t="n">
-        <v>339</v>
+        <v>136.96</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -24902,12 +25046,12 @@
       </c>
       <c r="M88" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7296</t>
+          <t>B5F7DF3C-7132</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Mbfxr1V40xsgbj8F0soExM05QND6zjoa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1n2bq_tMI3rNE2XsFpxvWnwo1ZZV6_K21/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24934,12 +25078,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" s="47" t="n">
-        <v>5</v>
+        <v>339</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -24955,7 +25099,7 @@
         <v>1</v>
       </c>
       <c r="K89" s="47" t="n">
-        <v>5</v>
+        <v>339</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -24964,12 +25108,12 @@
       </c>
       <c r="M89" s="49" t="inlineStr">
         <is>
-          <t>MC260002345804</t>
+          <t>B5F7DF3C-7296</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1WOvzAAmEygTW3UfGCE2EpvFGcNYl4yVq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Mbfxr1V40xsgbj8F0soExM05QND6zjoa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -24991,21 +25135,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>METAADS</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>eu</t>
-        </is>
-      </c>
+          <t>MASMOVIL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" s="47" t="n">
-        <v>15883.55</v>
+        <v>5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -25021,7 +25161,7 @@
         <v>1</v>
       </c>
       <c r="K90" s="47" t="n">
-        <v>15883.55</v>
+        <v>5</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -25030,12 +25170,12 @@
       </c>
       <c r="M90" s="49" t="inlineStr">
         <is>
-          <t>251380763</t>
+          <t>MC260002345804</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fDDyyoah7JlWMHXzqFDIqm2howZDBJMq/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1WOvzAAmEygTW3UfGCE2EpvFGcNYl4yVq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25067,11 +25207,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="G91" s="47" t="n">
-        <v>2794.04</v>
+        <v>15883.55</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -25087,7 +25227,7 @@
         <v>1</v>
       </c>
       <c r="K91" s="47" t="n">
-        <v>2794.04</v>
+        <v>15883.55</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -25133,11 +25273,11 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G92" s="47" t="n">
-        <v>1397.4</v>
+        <v>2794.04</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -25153,7 +25293,7 @@
         <v>1</v>
       </c>
       <c r="K92" s="47" t="n">
-        <v>1397.4</v>
+        <v>2794.04</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -25189,17 +25329,21 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G93" s="47" t="n">
-        <v>30.87</v>
+        <v>1397.4</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -25215,7 +25359,7 @@
         <v>1</v>
       </c>
       <c r="K93" s="47" t="n">
-        <v>30.87</v>
+        <v>1397.4</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -25224,12 +25368,12 @@
       </c>
       <c r="M93" s="49" t="inlineStr">
         <is>
-          <t>G140910268</t>
+          <t>251380763</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1IS2fSxolw6pxcI9vC65EJRYlFK7zyUTY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fDDyyoah7JlWMHXzqFDIqm2howZDBJMq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25261,7 +25405,7 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" s="47" t="n">
-        <v>47</v>
+        <v>30.87</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -25277,7 +25421,7 @@
         <v>1</v>
       </c>
       <c r="K94" s="47" t="n">
-        <v>47</v>
+        <v>30.87</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -25286,12 +25430,12 @@
       </c>
       <c r="M94" s="49" t="inlineStr">
         <is>
-          <t>G141681724</t>
+          <t>G140910268</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1najlnApOGpucn5h6ZtquKVucfInGLQ0V/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1IS2fSxolw6pxcI9vC65EJRYlFK7zyUTY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25318,20 +25462,16 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>api_usage</t>
-        </is>
-      </c>
+          <t>MICROSOFT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" s="47" t="n">
-        <v>10.03</v>
+        <v>47</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -25340,10 +25480,10 @@
         </is>
       </c>
       <c r="J95" s="48" t="n">
-        <v>0.84709869</v>
+        <v>1</v>
       </c>
       <c r="K95" s="47" t="n">
-        <v>8.5</v>
+        <v>47</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -25352,12 +25492,12 @@
       </c>
       <c r="M95" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0002</t>
+          <t>G141681724</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ia49BWDccoiY0_floiPgZIOoH73-LIUQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1najlnApOGpucn5h6ZtquKVucfInGLQ0V/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25393,7 +25533,7 @@
         </is>
       </c>
       <c r="G96" s="47" t="n">
-        <v>10.12</v>
+        <v>10.03</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -25409,7 +25549,7 @@
         <v>0.84709869</v>
       </c>
       <c r="K96" s="47" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -25418,12 +25558,12 @@
       </c>
       <c r="M96" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0003</t>
+          <t>BZHJNTUB0002</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1bbYR8-vHGj7nUKVcEnARnepPzYzNIFVw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ia49BWDccoiY0_floiPgZIOoH73-LIUQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25459,7 +25599,7 @@
         </is>
       </c>
       <c r="G97" s="47" t="n">
-        <v>10.19</v>
+        <v>10.12</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -25475,7 +25615,7 @@
         <v>0.84709869</v>
       </c>
       <c r="K97" s="47" t="n">
-        <v>8.630000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -25484,12 +25624,12 @@
       </c>
       <c r="M97" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0005</t>
+          <t>BZHJNTUB0003</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s-Ni6ccpvcuZUGwwhFepiSbUNzPwXVDG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1bbYR8-vHGj7nUKVcEnARnepPzYzNIFVw/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25525,7 +25665,7 @@
         </is>
       </c>
       <c r="G98" s="47" t="n">
-        <v>30</v>
+        <v>10.19</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -25541,7 +25681,7 @@
         <v>0.84709869</v>
       </c>
       <c r="K98" s="47" t="n">
-        <v>25.41</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -25550,12 +25690,12 @@
       </c>
       <c r="M98" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0006</t>
+          <t>BZHJNTUB0005</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j0GTnf9iA8T0YG7zocdvmE1v-yFf-dmk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s-Ni6ccpvcuZUGwwhFepiSbUNzPwXVDG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25731,7 @@
         </is>
       </c>
       <c r="G99" s="47" t="n">
-        <v>10.41</v>
+        <v>30</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -25607,7 +25747,7 @@
         <v>0.84709869</v>
       </c>
       <c r="K99" s="47" t="n">
-        <v>8.82</v>
+        <v>25.41</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -25616,12 +25756,12 @@
       </c>
       <c r="M99" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0007</t>
+          <t>BZHJNTUB0006</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1kgfYW187O8CHpqvovwje1T5Vb0O1df6d/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1j0GTnf9iA8T0YG7zocdvmE1v-yFf-dmk/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25653,11 +25793,11 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>receipt</t>
+          <t>api_usage</t>
         </is>
       </c>
       <c r="G100" s="47" t="n">
-        <v>10.13</v>
+        <v>10.41</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -25673,7 +25813,7 @@
         <v>0.84709869</v>
       </c>
       <c r="K100" s="47" t="n">
-        <v>8.58</v>
+        <v>8.82</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -25682,12 +25822,12 @@
       </c>
       <c r="M100" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0004</t>
+          <t>BZHJNTUB0007</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ylJiskEHkRFsuhK4EXI9Mv5Hk31tTSeX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1kgfYW187O8CHpqvovwje1T5Vb0O1df6d/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25704,26 +25844,30 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>PRESSING</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>receipt</t>
+        </is>
+      </c>
       <c r="G101" s="47" t="n">
-        <v>33510.62</v>
+        <v>10.13</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -25732,10 +25876,10 @@
         </is>
       </c>
       <c r="J101" s="48" t="n">
-        <v>1</v>
+        <v>0.84709869</v>
       </c>
       <c r="K101" s="47" t="n">
-        <v>33510.62</v>
+        <v>8.58</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -25744,12 +25888,12 @@
       </c>
       <c r="M101" s="49" t="inlineStr">
         <is>
-          <t>FAC/2026/26100001651</t>
+          <t>BZHJNTUB0004</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Ht3FP9y_KBG3F1Wui0f7dj36Nz4gORY9/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ylJiskEHkRFsuhK4EXI9Mv5Hk31tTSeX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25766,22 +25910,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>PRESSING</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" s="47" t="n">
-        <v>134</v>
+        <v>33510.62</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -25797,7 +25941,7 @@
         <v>1</v>
       </c>
       <c r="K102" s="47" t="n">
-        <v>134</v>
+        <v>33510.62</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -25806,12 +25950,12 @@
       </c>
       <c r="M102" s="49" t="inlineStr">
         <is>
-          <t>211723</t>
+          <t>FAC/2026/26100001651</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1axe5iqNHDnZKEyTVyAhJ5hBtI1BR5ejL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Ht3FP9y_KBG3F1Wui0f7dj36Nz4gORY9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25838,12 +25982,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" s="47" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -25859,7 +26003,7 @@
         <v>1</v>
       </c>
       <c r="K103" s="47" t="n">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -25868,12 +26012,12 @@
       </c>
       <c r="M103" s="49" t="inlineStr">
         <is>
-          <t>RVR-17688</t>
+          <t>211723</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D3oOwMbnoMx_ZwdzSUQ07lRdDelVCXX6/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1axe5iqNHDnZKEyTVyAhJ5hBtI1BR5ejL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25900,16 +26044,16 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" s="47" t="n">
-        <v>2812.25</v>
+        <v>79</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -25918,10 +26062,10 @@
         </is>
       </c>
       <c r="J104" s="48" t="n">
-        <v>0.84709869</v>
+        <v>1</v>
       </c>
       <c r="K104" s="47" t="n">
-        <v>2382.25</v>
+        <v>79</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -25930,12 +26074,12 @@
       </c>
       <c r="M104" s="49" t="inlineStr">
         <is>
-          <t>493806587</t>
+          <t>RVR-17688</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FNZalAzXj8a7ZNUt2CefEIFu_sLZ6iOY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D3oOwMbnoMx_ZwdzSUQ07lRdDelVCXX6/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25957,21 +26101,21 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" s="47" t="n">
-        <v>15</v>
+        <v>2812.25</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -25980,10 +26124,10 @@
         </is>
       </c>
       <c r="J105" s="48" t="n">
-        <v>1</v>
+        <v>0.84709869</v>
       </c>
       <c r="K105" s="47" t="n">
-        <v>15</v>
+        <v>2382.25</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -25992,12 +26136,12 @@
       </c>
       <c r="M105" s="49" t="inlineStr">
         <is>
-          <t>7/517</t>
+          <t>493806587</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ryYPmeaeN0WBdXxhk4O9pmdF4BlNsACt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FNZalAzXj8a7ZNUt2CefEIFu_sLZ6iOY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26014,22 +26158,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" s="47" t="n">
-        <v>643.8200000000001</v>
+        <v>15</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -26045,7 +26189,7 @@
         <v>1</v>
       </c>
       <c r="K106" s="47" t="n">
-        <v>643.8200000000001</v>
+        <v>15</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -26054,12 +26198,12 @@
       </c>
       <c r="M106" s="49" t="inlineStr">
         <is>
-          <t>326997856</t>
+          <t>7/517</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FyBHZEA9qWMwRhMfdTuL7ySwcplaqQc2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ryYPmeaeN0WBdXxhk4O9pmdF4BlNsACt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26091,7 +26235,7 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" s="47" t="n">
-        <v>629.73</v>
+        <v>643.8200000000001</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -26107,7 +26251,7 @@
         <v>1</v>
       </c>
       <c r="K107" s="47" t="n">
-        <v>629.73</v>
+        <v>643.8200000000001</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -26116,12 +26260,12 @@
       </c>
       <c r="M107" s="49" t="inlineStr">
         <is>
-          <t>327030108</t>
+          <t>326997856</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1iPkhcnUQ6IlOI2t9Y4lt6fcN9NoE8559/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1FyBHZEA9qWMwRhMfdTuL7ySwcplaqQc2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26297,7 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" s="47" t="n">
-        <v>512.62</v>
+        <v>629.73</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -26169,7 +26313,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="47" t="n">
-        <v>512.62</v>
+        <v>629.73</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -26178,12 +26322,12 @@
       </c>
       <c r="M108" s="49" t="inlineStr">
         <is>
-          <t>327061645</t>
+          <t>327030108</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nrrH_8TfwdiHGNLlFgfu6hEx8mBDTA67/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1iPkhcnUQ6IlOI2t9Y4lt6fcN9NoE8559/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26215,7 +26359,7 @@
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" s="47" t="n">
-        <v>40.32</v>
+        <v>512.62</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -26231,7 +26375,7 @@
         <v>1</v>
       </c>
       <c r="K109" s="47" t="n">
-        <v>40.32</v>
+        <v>512.62</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -26240,12 +26384,12 @@
       </c>
       <c r="M109" s="49" t="inlineStr">
         <is>
-          <t>838088024</t>
+          <t>327061645</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Lq08NNbxsMBp7B7MMjUiEknDIr3kxPc0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nrrH_8TfwdiHGNLlFgfu6hEx8mBDTA67/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26262,22 +26406,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" s="47" t="n">
-        <v>440</v>
+        <v>40.32</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -26293,7 +26437,7 @@
         <v>1</v>
       </c>
       <c r="K110" s="47" t="n">
-        <v>440</v>
+        <v>40.32</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -26302,19 +26446,19 @@
       </c>
       <c r="M110" s="49" t="inlineStr">
         <is>
-          <t>OQXBYXMP-0005</t>
+          <t>838088024</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y53mv0-BjFCp7Z4Tp9mguo1WuS7RRlVK/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Lq08NNbxsMBp7B7MMjUiEknDIr3kxPc0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -26334,12 +26478,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" s="47" t="n">
-        <v>33.49</v>
+        <v>440</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -26355,7 +26499,7 @@
         <v>1</v>
       </c>
       <c r="K111" s="47" t="n">
-        <v>33.49</v>
+        <v>440</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -26364,12 +26508,12 @@
       </c>
       <c r="M111" s="49" t="inlineStr">
         <is>
-          <t>IEE2026005856850</t>
+          <t>OQXBYXMP-0005</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_QV16SfnrecVZCv19siScEIbSVNhcwQY/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y53mv0-BjFCp7Z4Tp9mguo1WuS7RRlVK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26386,22 +26530,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>APPHOTOCAN</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" s="47" t="n">
-        <v>116.57</v>
+        <v>33.49</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -26417,7 +26561,7 @@
         <v>1</v>
       </c>
       <c r="K112" s="47" t="n">
-        <v>116.57</v>
+        <v>33.49</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -26426,12 +26570,12 @@
       </c>
       <c r="M112" s="49" t="inlineStr">
         <is>
-          <t>26-1-600</t>
+          <t>IEE2026005856850</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1U8O1YcuZmCf_avd7RanqWgUAXL733mJ4/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_QV16SfnrecVZCv19siScEIbSVNhcwQY/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26458,12 +26602,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>APPHOTOES</t>
+          <t>APPHOTOCAN</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" s="47" t="n">
-        <v>697.99</v>
+        <v>116.57</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -26479,7 +26623,7 @@
         <v>1</v>
       </c>
       <c r="K113" s="47" t="n">
-        <v>697.99</v>
+        <v>116.57</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -26488,12 +26632,12 @@
       </c>
       <c r="M113" s="49" t="inlineStr">
         <is>
-          <t>1-2805</t>
+          <t>26-1-600</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1n1TdGRm0xbbUrhiWxso3ucgcPhj4jbzx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1U8O1YcuZmCf_avd7RanqWgUAXL733mJ4/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26525,7 +26669,7 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" s="47" t="n">
-        <v>26.57</v>
+        <v>697.99</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -26541,7 +26685,7 @@
         <v>1</v>
       </c>
       <c r="K114" s="47" t="n">
-        <v>26.57</v>
+        <v>697.99</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -26550,12 +26694,12 @@
       </c>
       <c r="M114" s="49" t="inlineStr">
         <is>
-          <t>1-2806</t>
+          <t>1-2805</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ao5r16qm7GhBSrW3YeiF3erPmxlcHELA/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1n1TdGRm0xbbUrhiWxso3ucgcPhj4jbzx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26587,7 +26731,7 @@
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" s="47" t="n">
-        <v>150.61</v>
+        <v>26.57</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -26603,7 +26747,7 @@
         <v>1</v>
       </c>
       <c r="K115" s="47" t="n">
-        <v>150.61</v>
+        <v>26.57</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -26612,12 +26756,12 @@
       </c>
       <c r="M115" s="49" t="inlineStr">
         <is>
-          <t>1-2807</t>
+          <t>1-2806</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OXbTejlLlT9SzZTWZP1D7tU57XBkfsLB/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ao5r16qm7GhBSrW3YeiF3erPmxlcHELA/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26649,7 +26793,7 @@
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" s="47" t="n">
-        <v>35.45</v>
+        <v>150.61</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -26665,7 +26809,7 @@
         <v>1</v>
       </c>
       <c r="K116" s="47" t="n">
-        <v>35.45</v>
+        <v>150.61</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -26674,12 +26818,12 @@
       </c>
       <c r="M116" s="49" t="inlineStr">
         <is>
-          <t>1-2808</t>
+          <t>1-2807</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1-0D2m0NVI4A5J-ddmlF3nafsBa8vGWBd/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1OXbTejlLlT9SzZTWZP1D7tU57XBkfsLB/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26711,7 +26855,7 @@
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" s="47" t="n">
-        <v>18.45</v>
+        <v>35.45</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -26727,7 +26871,7 @@
         <v>1</v>
       </c>
       <c r="K117" s="47" t="n">
-        <v>18.45</v>
+        <v>35.45</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -26736,12 +26880,12 @@
       </c>
       <c r="M117" s="49" t="inlineStr">
         <is>
-          <t>1-2809</t>
+          <t>1-2808</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/109FoRS20p6fG5cg4HRHkxTwOGMiEB3AH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-0D2m0NVI4A5J-ddmlF3nafsBa8vGWBd/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26917,7 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" s="47" t="n">
-        <v>6244.25</v>
+        <v>18.45</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -26789,7 +26933,7 @@
         <v>1</v>
       </c>
       <c r="K118" s="47" t="n">
-        <v>6244.25</v>
+        <v>18.45</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -26798,12 +26942,12 @@
       </c>
       <c r="M118" s="49" t="inlineStr">
         <is>
-          <t>1-2921</t>
+          <t>1-2809</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1md630rqHnAw6S5fnMiH86ktIGL9wAfgF/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/109FoRS20p6fG5cg4HRHkxTwOGMiEB3AH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26835,7 +26979,7 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" s="47" t="n">
-        <v>4435.99</v>
+        <v>6244.25</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -26851,7 +26995,7 @@
         <v>1</v>
       </c>
       <c r="K119" s="47" t="n">
-        <v>4435.99</v>
+        <v>6244.25</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -26860,12 +27004,12 @@
       </c>
       <c r="M119" s="49" t="inlineStr">
         <is>
-          <t>1-3283</t>
+          <t>1-2921</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MkhCT3OZenS4bJf5_J2qB8oGGw8oFzkf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1md630rqHnAw6S5fnMiH86ktIGL9wAfgF/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26897,7 +27041,7 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" s="47" t="n">
-        <v>3843.26</v>
+        <v>4435.99</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -26913,7 +27057,7 @@
         <v>1</v>
       </c>
       <c r="K120" s="47" t="n">
-        <v>3843.26</v>
+        <v>4435.99</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -26922,12 +27066,12 @@
       </c>
       <c r="M120" s="49" t="inlineStr">
         <is>
-          <t>1-3565</t>
+          <t>1-3283</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19nt9_Pc7ZLzBMkh9rxX3ashw6fPaDBG_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MkhCT3OZenS4bJf5_J2qB8oGGw8oFzkf/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -26959,7 +27103,7 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" s="47" t="n">
-        <v>5825.41</v>
+        <v>3843.26</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -26975,7 +27119,7 @@
         <v>1</v>
       </c>
       <c r="K121" s="47" t="n">
-        <v>5825.41</v>
+        <v>3843.26</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -26984,12 +27128,12 @@
       </c>
       <c r="M121" s="49" t="inlineStr">
         <is>
-          <t>1-3959</t>
+          <t>1-3565</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qmdVuUyZKvATz7DKzN55oORVw6pAX9mO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19nt9_Pc7ZLzBMkh9rxX3ashw6fPaDBG_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27016,16 +27160,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>ARTLINK</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>manufacturing</t>
-        </is>
-      </c>
+          <t>APPHOTOES</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" s="47" t="n">
-        <v>570</v>
+        <v>5825.41</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -27041,7 +27181,7 @@
         <v>1</v>
       </c>
       <c r="K122" s="47" t="n">
-        <v>570</v>
+        <v>5825.41</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -27050,12 +27190,12 @@
       </c>
       <c r="M122" s="49" t="inlineStr">
         <is>
-          <t>000203570</t>
+          <t>1-3959</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1cfzsuLvXSAtRD2pLnRBZ59veQeIWQKjQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qmdVuUyZKvATz7DKzN55oORVw6pAX9mO/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27072,22 +27212,26 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CANVA</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>ARTLINK</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
       <c r="G123" s="47" t="n">
-        <v>9.91</v>
+        <v>570</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -27103,7 +27247,7 @@
         <v>1</v>
       </c>
       <c r="K123" s="47" t="n">
-        <v>9.91</v>
+        <v>570</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -27112,12 +27256,12 @@
       </c>
       <c r="M123" s="49" t="inlineStr">
         <is>
-          <t>04824-31033212</t>
+          <t>000203570</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Bt_uYId0Ke_7yyUlyt95NlsppeCL3W_F/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1cfzsuLvXSAtRD2pLnRBZ59veQeIWQKjQ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27139,17 +27283,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" s="47" t="n">
-        <v>808.08</v>
+        <v>9.91</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -27165,7 +27309,7 @@
         <v>1</v>
       </c>
       <c r="K124" s="47" t="n">
-        <v>808.08</v>
+        <v>9.91</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -27174,12 +27318,12 @@
       </c>
       <c r="M124" s="49" t="inlineStr">
         <is>
-          <t>F00658/26</t>
+          <t>04824-31033212</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/194sPXt7bz4RYudtr1LLnRSTHRD3IRfX_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Bt_uYId0Ke_7yyUlyt95NlsppeCL3W_F/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27206,12 +27350,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CONTASIMPLE</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" s="47" t="n">
-        <v>191.4</v>
+        <v>808.08</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -27227,7 +27371,7 @@
         <v>1</v>
       </c>
       <c r="K125" s="47" t="n">
-        <v>191.4</v>
+        <v>808.08</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -27236,12 +27380,12 @@
       </c>
       <c r="M125" s="49" t="inlineStr">
         <is>
-          <t>ES-2026-11348</t>
+          <t>F00658/26</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Kf3zLbAifsK47hwsfDtdiya2nTjoZhbc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/194sPXt7bz4RYudtr1LLnRSTHRD3IRfX_/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27258,22 +27402,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CORREOS</t>
+          <t>CONTASIMPLE</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" s="47" t="n">
-        <v>193.8</v>
+        <v>191.4</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -27289,7 +27433,7 @@
         <v>1</v>
       </c>
       <c r="K126" s="47" t="n">
-        <v>193.8</v>
+        <v>191.4</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -27298,12 +27442,12 @@
       </c>
       <c r="M126" s="49" t="inlineStr">
         <is>
-          <t>4004641446</t>
+          <t>ES-2026-11348</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19BOJcU-tZOdXNewpB9MmZXKbUeYoLmQW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Kf3zLbAifsK47hwsfDtdiya2nTjoZhbc/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27330,12 +27474,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CORREOSCAN</t>
+          <t>CORREOS</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" s="47" t="n">
-        <v>8.83</v>
+        <v>193.8</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -27351,7 +27495,7 @@
         <v>1</v>
       </c>
       <c r="K127" s="47" t="n">
-        <v>8.83</v>
+        <v>193.8</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -27360,12 +27504,12 @@
       </c>
       <c r="M127" s="49" t="inlineStr">
         <is>
-          <t>4004641447</t>
+          <t>4004641446</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1OSsPTK_eKr03kWPWfsduaZWbO-PcRSKN/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19BOJcU-tZOdXNewpB9MmZXKbUeYoLmQW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27387,17 +27531,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>CORREOSCAN</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" s="47" t="n">
-        <v>2646.66</v>
+        <v>8.83</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -27413,7 +27557,7 @@
         <v>1</v>
       </c>
       <c r="K128" s="47" t="n">
-        <v>2646.66</v>
+        <v>8.83</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -27422,12 +27566,12 @@
       </c>
       <c r="M128" s="49" t="inlineStr">
         <is>
-          <t>26-0463</t>
+          <t>4004641447</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1d9bGOdNerfRkG8hm-9tNwNLOClNoUKV1/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1OSsPTK_eKr03kWPWfsduaZWbO-PcRSKN/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27459,7 +27603,7 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" s="47" t="n">
-        <v>2854.58</v>
+        <v>2646.66</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -27475,7 +27619,7 @@
         <v>1</v>
       </c>
       <c r="K129" s="47" t="n">
-        <v>2854.58</v>
+        <v>2646.66</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -27484,12 +27628,12 @@
       </c>
       <c r="M129" s="49" t="inlineStr">
         <is>
-          <t>26-0548</t>
+          <t>26-0463</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1RN40IgZT0khKxDgZ1TciqcREU1AzC6iG/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1d9bGOdNerfRkG8hm-9tNwNLOClNoUKV1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27511,17 +27655,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" s="47" t="n">
-        <v>14170.85</v>
+        <v>2854.58</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -27537,7 +27681,7 @@
         <v>1</v>
       </c>
       <c r="K130" s="47" t="n">
-        <v>14170.85</v>
+        <v>2854.58</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -27546,12 +27690,12 @@
       </c>
       <c r="M130" s="49" t="inlineStr">
         <is>
-          <t>20260150</t>
+          <t>26-0548</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Fys_Ke3o0S3pZkqtEQkaOmeaEm-sTj0X/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1RN40IgZT0khKxDgZ1TciqcREU1AzC6iG/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27568,22 +27712,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" s="47" t="n">
-        <v>13.11</v>
+        <v>14170.85</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -27599,7 +27743,7 @@
         <v>1</v>
       </c>
       <c r="K131" s="47" t="n">
-        <v>13.11</v>
+        <v>14170.85</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -27608,12 +27752,12 @@
       </c>
       <c r="M131" s="49" t="inlineStr">
         <is>
-          <t>4046950709</t>
+          <t>20260150</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1mhP1xnzmk8CIu8lzS9UTKi1YVgQ0j5vD/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Fys_Ke3o0S3pZkqtEQkaOmeaEm-sTj0X/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27645,7 +27789,7 @@
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" s="47" t="n">
-        <v>21.99</v>
+        <v>13.11</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -27661,7 +27805,7 @@
         <v>1</v>
       </c>
       <c r="K132" s="47" t="n">
-        <v>21.99</v>
+        <v>13.11</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -27670,12 +27814,12 @@
       </c>
       <c r="M132" s="49" t="inlineStr">
         <is>
-          <t>4048729358</t>
+          <t>4046950709</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1EeQh_f0ge3L2vpmoZhGqULVvQDnFYlXt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1mhP1xnzmk8CIu8lzS9UTKi1YVgQ0j5vD/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27697,21 +27841,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>eu</t>
-        </is>
-      </c>
+          <t>GODADDY</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" s="47" t="n">
-        <v>24360.27</v>
+        <v>21.99</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -27727,7 +27867,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="47" t="n">
-        <v>24360.27</v>
+        <v>21.99</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -27736,12 +27876,12 @@
       </c>
       <c r="M133" s="49" t="inlineStr">
         <is>
-          <t>5538547928</t>
+          <t>4048729358</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1s7eUjqGV_ux0WxJrpYLtGKjjOS3f9F_q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1EeQh_f0ge3L2vpmoZhGqULVvQDnFYlXt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27773,11 +27913,11 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="G134" s="47" t="n">
-        <v>5956.59</v>
+        <v>24360.27</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -27793,7 +27933,7 @@
         <v>1</v>
       </c>
       <c r="K134" s="47" t="n">
-        <v>5956.59</v>
+        <v>24360.27</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -27839,11 +27979,11 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G135" s="47" t="n">
-        <v>3341.56</v>
+        <v>5956.59</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -27859,7 +27999,7 @@
         <v>1</v>
       </c>
       <c r="K135" s="47" t="n">
-        <v>3341.56</v>
+        <v>5956.59</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -27895,17 +28035,21 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G136" s="47" t="n">
-        <v>210.6</v>
+        <v>3341.56</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -27921,7 +28065,7 @@
         <v>1</v>
       </c>
       <c r="K136" s="47" t="n">
-        <v>210.6</v>
+        <v>3341.56</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -27930,12 +28074,12 @@
       </c>
       <c r="M136" s="49" t="inlineStr">
         <is>
-          <t>5528949048</t>
+          <t>5538547928</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1l-tObm8vyP3XyPss2x7ZU0ypwypzolZi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1s7eUjqGV_ux0WxJrpYLtGKjjOS3f9F_q/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -27962,16 +28106,16 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" s="47" t="n">
-        <v>126.4</v>
+        <v>210.6</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -27980,10 +28124,10 @@
         </is>
       </c>
       <c r="J137" s="48" t="n">
-        <v>0.86971647</v>
+        <v>1</v>
       </c>
       <c r="K137" s="47" t="n">
-        <v>109.93</v>
+        <v>210.6</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -27992,12 +28136,12 @@
       </c>
       <c r="M137" s="49" t="inlineStr">
         <is>
-          <t>INC-03-2026-64889</t>
+          <t>5528949048</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1r5NeAkt6BuK7stM77wMD2GmwfOkmyuaE/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1l-tObm8vyP3XyPss2x7ZU0ypwypzolZi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28019,25 +28163,21 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HANNUN</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
+          <t>GORGIAS</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" s="47" t="n">
-        <v>30</v>
+        <v>126.4</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -28046,10 +28186,10 @@
         </is>
       </c>
       <c r="J138" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K138" s="47" t="n">
-        <v>30</v>
+        <v>109.93</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -28058,12 +28198,12 @@
       </c>
       <c r="M138" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-010337</t>
+          <t>INC-03-2026-64889</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1jBhJD7kS5_SPwJKWbOaHjrF8mX4mpiT8/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1r5NeAkt6BuK7stM77wMD2GmwfOkmyuaE/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28095,11 +28235,11 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="G139" s="47" t="n">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -28115,7 +28255,7 @@
         <v>1</v>
       </c>
       <c r="K139" s="47" t="n">
-        <v>175</v>
+        <v>30</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -28124,12 +28264,12 @@
       </c>
       <c r="M139" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-012333</t>
+          <t>VTA/26-010337</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1y_VFTA5on6ReO79xvnlu0N3xL-BbnpEM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1jBhJD7kS5_SPwJKWbOaHjrF8mX4mpiT8/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28161,11 +28301,11 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>services</t>
+          <t>office</t>
         </is>
       </c>
       <c r="G140" s="47" t="n">
-        <v>1165.1</v>
+        <v>175</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -28181,7 +28321,7 @@
         <v>1</v>
       </c>
       <c r="K140" s="47" t="n">
-        <v>1165.1</v>
+        <v>175</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -28190,12 +28330,12 @@
       </c>
       <c r="M140" s="49" t="inlineStr">
         <is>
-          <t>VTA/26-012334</t>
+          <t>VTA/26-012333</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1BXJcbamEE34UrEHgJabkn3cuDfiFSgXJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1y_VFTA5on6ReO79xvnlu0N3xL-BbnpEM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28217,17 +28357,21 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>services</t>
+        </is>
+      </c>
       <c r="G141" s="47" t="n">
-        <v>182.45</v>
+        <v>1165.1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -28243,7 +28387,7 @@
         <v>1</v>
       </c>
       <c r="K141" s="47" t="n">
-        <v>182.45</v>
+        <v>1165.1</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -28252,12 +28396,12 @@
       </c>
       <c r="M141" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7472</t>
+          <t>VTA/26-012334</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nWo-mNGMmMRAWJEGmVLJaMtqo73kBgzv/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1BXJcbamEE34UrEHgJabkn3cuDfiFSgXJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28289,7 +28433,7 @@
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" s="47" t="n">
-        <v>339</v>
+        <v>182.45</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -28305,7 +28449,7 @@
         <v>1</v>
       </c>
       <c r="K142" s="47" t="n">
-        <v>339</v>
+        <v>182.45</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -28314,12 +28458,12 @@
       </c>
       <c r="M142" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7629</t>
+          <t>B5F7DF3C-7472</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CqOn2Zx8mbhJOVhiMIiGbOghQnA3vTDp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1nWo-mNGMmMRAWJEGmVLJaMtqo73kBgzv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28351,7 +28495,7 @@
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" s="47" t="n">
-        <v>60.44</v>
+        <v>339</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -28367,7 +28511,7 @@
         <v>1</v>
       </c>
       <c r="K143" s="47" t="n">
-        <v>60.44</v>
+        <v>339</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -28376,12 +28520,12 @@
       </c>
       <c r="M143" s="49" t="inlineStr">
         <is>
-          <t>B5F7DF3C-7709</t>
+          <t>B5F7DF3C-7629</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ECBhz1VCwbBVoxwkdm3YFSwEGxpN8nXX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CqOn2Zx8mbhJOVhiMIiGbOghQnA3vTDp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28408,12 +28552,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" s="47" t="n">
-        <v>8.83</v>
+        <v>60.44</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -28429,7 +28573,7 @@
         <v>1</v>
       </c>
       <c r="K144" s="47" t="n">
-        <v>8.83</v>
+        <v>60.44</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -28438,12 +28582,12 @@
       </c>
       <c r="M144" s="49" t="inlineStr">
         <is>
-          <t>MC260003336170</t>
+          <t>B5F7DF3C-7709</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/18aHMUoONC6SlndhHYF_AWRN3TCOoVrvg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ECBhz1VCwbBVoxwkdm3YFSwEGxpN8nXX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28465,21 +28609,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>METAADS</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>eu</t>
-        </is>
-      </c>
+          <t>MASMOVIL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" s="47" t="n">
-        <v>17635.61</v>
+        <v>8.83</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -28495,7 +28635,7 @@
         <v>1</v>
       </c>
       <c r="K145" s="47" t="n">
-        <v>17635.61</v>
+        <v>8.83</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -28504,12 +28644,12 @@
       </c>
       <c r="M145" s="49" t="inlineStr">
         <is>
-          <t>251912684</t>
+          <t>MC260003336170</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/18aHMUoONC6SlndhHYF_AWRN3TCOoVrvg/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28541,11 +28681,11 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="G146" s="47" t="n">
-        <v>2970.18</v>
+        <v>17635.61</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -28561,7 +28701,7 @@
         <v>1</v>
       </c>
       <c r="K146" s="47" t="n">
-        <v>2970.18</v>
+        <v>17635.61</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -28607,11 +28747,11 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G147" s="47" t="n">
-        <v>1317.27</v>
+        <v>2970.18</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -28627,7 +28767,7 @@
         <v>1</v>
       </c>
       <c r="K147" s="47" t="n">
-        <v>1317.27</v>
+        <v>2970.18</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -28663,17 +28803,21 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G148" s="47" t="n">
-        <v>30.87</v>
+        <v>1317.27</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -28689,7 +28833,7 @@
         <v>1</v>
       </c>
       <c r="K148" s="47" t="n">
-        <v>30.87</v>
+        <v>1317.27</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -28698,12 +28842,12 @@
       </c>
       <c r="M148" s="49" t="inlineStr">
         <is>
-          <t>G146754373</t>
+          <t>251912684</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1DCPq5CCQbxKn8xbE5ConsRttwki8sRoJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1g1NqMXMRnrd3ujXFvvHnpVryss1CmF5D/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28735,7 +28879,7 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" s="47" t="n">
-        <v>45.7</v>
+        <v>30.87</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -28751,7 +28895,7 @@
         <v>1</v>
       </c>
       <c r="K149" s="47" t="n">
-        <v>45.7</v>
+        <v>30.87</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -28760,12 +28904,12 @@
       </c>
       <c r="M149" s="49" t="inlineStr">
         <is>
-          <t>G147511406</t>
+          <t>G146754373</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1j0AP8BcSvjbMkHqbG0jNHzXuXksgaBTp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1DCPq5CCQbxKn8xbE5ConsRttwki8sRoJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28792,20 +28936,16 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>OPENAI</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>api_usage</t>
-        </is>
-      </c>
+          <t>MICROSOFT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" s="47" t="n">
-        <v>15</v>
+        <v>45.7</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -28814,10 +28954,10 @@
         </is>
       </c>
       <c r="J150" s="48" t="n">
-        <v>0.86971647</v>
+        <v>1</v>
       </c>
       <c r="K150" s="47" t="n">
-        <v>13.05</v>
+        <v>45.7</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -28826,12 +28966,12 @@
       </c>
       <c r="M150" s="49" t="inlineStr">
         <is>
-          <t>BZHJNTUB0008</t>
+          <t>G147511406</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/14mLVYewapKRBwsNP7f6wLOc4WRmROQLm/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1j0AP8BcSvjbMkHqbG0jNHzXuXksgaBTp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28848,26 +28988,30 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PRESSING</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>api_usage</t>
+        </is>
+      </c>
       <c r="G151" s="47" t="n">
-        <v>30382.03</v>
+        <v>15</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -28876,10 +29020,10 @@
         </is>
       </c>
       <c r="J151" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K151" s="47" t="n">
-        <v>30382.03</v>
+        <v>13.05</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -28888,12 +29032,12 @@
       </c>
       <c r="M151" s="49" t="inlineStr">
         <is>
-          <t>FAC/2026/26100002919</t>
+          <t>BZHJNTUB0008</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NnctdjrWo_YQUOWmOChF9VEkLKCvwH7r/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14mLVYewapKRBwsNP7f6wLOc4WRmROQLm/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28925,7 +29069,7 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" s="47" t="n">
-        <v>-15135.51</v>
+        <v>30382.03</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -28941,7 +29085,7 @@
         <v>1</v>
       </c>
       <c r="K152" s="47" t="n">
-        <v>-15135.51</v>
+        <v>30382.03</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -28950,12 +29094,12 @@
       </c>
       <c r="M152" s="49" t="inlineStr">
         <is>
-          <t>REC/2026/26200000052</t>
+          <t>FAC/2026/26100002919</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1AS6ZaTkoyH52MXQbp1lIDdFsAOEBnPum/view</t>
+          <t>https://drive.google.com/file/d/1NnctdjrWo_YQUOWmOChF9VEkLKCvwH7r/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -28972,22 +29116,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>PRESSING</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" s="47" t="n">
-        <v>134</v>
+        <v>-15135.51</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -29003,7 +29147,7 @@
         <v>1</v>
       </c>
       <c r="K153" s="47" t="n">
-        <v>134</v>
+        <v>-15135.51</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -29012,12 +29156,12 @@
       </c>
       <c r="M153" s="49" t="inlineStr">
         <is>
-          <t>217905</t>
+          <t>REC/2026/26200000052</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1q5GM5mcOxTlAfTEBbnsDgygc2l8igChV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1AS6ZaTkoyH52MXQbp1lIDdFsAOEBnPum/view</t>
         </is>
       </c>
     </row>
@@ -29044,16 +29188,16 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" s="47" t="n">
-        <v>21.36</v>
+        <v>134</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -29062,10 +29206,10 @@
         </is>
       </c>
       <c r="J154" s="48" t="n">
-        <v>0.86971647</v>
+        <v>1</v>
       </c>
       <c r="K154" s="47" t="n">
-        <v>18.58</v>
+        <v>134</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -29074,12 +29218,12 @@
       </c>
       <c r="M154" s="49" t="inlineStr">
         <is>
-          <t>1602C2F5-0017</t>
+          <t>217905</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1_zSaGhAEICAUBmqreT7FKVxXgv2-r3jW/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1q5GM5mcOxTlAfTEBbnsDgygc2l8igChV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29106,16 +29250,16 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" s="47" t="n">
-        <v>436.38</v>
+        <v>21.36</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -29124,10 +29268,10 @@
         </is>
       </c>
       <c r="J155" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K155" s="47" t="n">
-        <v>436.38</v>
+        <v>18.58</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -29136,12 +29280,12 @@
       </c>
       <c r="M155" s="49" t="inlineStr">
         <is>
-          <t>RVR-17393</t>
+          <t>1602C2F5-0017</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CWhfJHSOw1n7f9t5k-dWx1KXNq0OtlHl/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1_zSaGhAEICAUBmqreT7FKVxXgv2-r3jW/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29173,7 +29317,7 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" s="47" t="n">
-        <v>299.89</v>
+        <v>436.38</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -29189,7 +29333,7 @@
         <v>1</v>
       </c>
       <c r="K156" s="47" t="n">
-        <v>299.89</v>
+        <v>436.38</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -29198,12 +29342,12 @@
       </c>
       <c r="M156" s="49" t="inlineStr">
         <is>
-          <t>RVR-18216</t>
+          <t>RVR-17393</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ugF3jSpFNoCK5W7nlv4RnQWYri-rwsCH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CWhfJHSOw1n7f9t5k-dWx1KXNq0OtlHl/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29235,7 +29379,7 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" s="47" t="n">
-        <v>79</v>
+        <v>299.89</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -29251,7 +29395,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="47" t="n">
-        <v>79</v>
+        <v>299.89</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -29260,12 +29404,12 @@
       </c>
       <c r="M157" s="49" t="inlineStr">
         <is>
-          <t>RVR-18566</t>
+          <t>RVR-18216</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dHhK1m1wSqKZeeNradd6kO_U1yP4OEZx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ugF3jSpFNoCK5W7nlv4RnQWYri-rwsCH/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29292,16 +29436,16 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" s="47" t="n">
-        <v>3223.43</v>
+        <v>79</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -29310,10 +29454,10 @@
         </is>
       </c>
       <c r="J158" s="48" t="n">
-        <v>0.86971647</v>
+        <v>1</v>
       </c>
       <c r="K158" s="47" t="n">
-        <v>2803.47</v>
+        <v>79</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -29322,12 +29466,12 @@
       </c>
       <c r="M158" s="49" t="inlineStr">
         <is>
-          <t>506718743</t>
+          <t>RVR-18566</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1ZCs5X4Qp9kY8mI50ovA19IzFEuYf6xco/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dHhK1m1wSqKZeeNradd6kO_U1yP4OEZx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29354,12 +29498,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" s="47" t="n">
-        <v>24.99</v>
+        <v>3223.43</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -29375,7 +29519,7 @@
         <v>0.86971647</v>
       </c>
       <c r="K159" s="47" t="n">
-        <v>21.73</v>
+        <v>2803.47</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -29384,12 +29528,12 @@
       </c>
       <c r="M159" s="49" t="inlineStr">
         <is>
-          <t>TADGCDFS-0001</t>
+          <t>506718743</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1PjQXXRgJWle6bvVGYUn8W3Swp9IqcBqL/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZCs5X4Qp9kY8mI50ovA19IzFEuYf6xco/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29446,12 +29590,12 @@
       </c>
       <c r="M160" s="49" t="inlineStr">
         <is>
-          <t>TADGCDFS-0002</t>
+          <t>TADGCDFS-0001</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1dZC3fsBfen5iERm3x2JFrd1LGddt0qLb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1PjQXXRgJWle6bvVGYUn8W3Swp9IqcBqL/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29508,12 +29652,12 @@
       </c>
       <c r="M161" s="49" t="inlineStr">
         <is>
-          <t>TADGCDFS-0003</t>
+          <t>TADGCDFS-0002</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/19CqsBdkfVuCtWYJwUtZxWcPjUVgdtwXa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1dZC3fsBfen5iERm3x2JFrd1LGddt0qLb/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29535,21 +29679,21 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" s="47" t="n">
-        <v>15</v>
+        <v>24.99</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -29558,10 +29702,10 @@
         </is>
       </c>
       <c r="J162" s="48" t="n">
-        <v>1</v>
+        <v>0.86971647</v>
       </c>
       <c r="K162" s="47" t="n">
-        <v>15</v>
+        <v>21.73</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -29570,12 +29714,12 @@
       </c>
       <c r="M162" s="49" t="inlineStr">
         <is>
-          <t>7/800</t>
+          <t>TADGCDFS-0003</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1qLKvi2Ja2apUNKYZBiLqZTt00IfYF7J2/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/19CqsBdkfVuCtWYJwUtZxWcPjUVgdtwXa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29592,22 +29736,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" s="47" t="n">
-        <v>723.1799999999999</v>
+        <v>15</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -29623,7 +29767,7 @@
         <v>1</v>
       </c>
       <c r="K163" s="47" t="n">
-        <v>723.1799999999999</v>
+        <v>15</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -29632,12 +29776,12 @@
       </c>
       <c r="M163" s="49" t="inlineStr">
         <is>
-          <t>327127415</t>
+          <t>7/800</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1szeFukWcwJsTpYUKLKIKWZXLhy2sel8E/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1qLKvi2Ja2apUNKYZBiLqZTt00IfYF7J2/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29669,7 +29813,7 @@
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" s="47" t="n">
-        <v>401.71</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -29685,7 +29829,7 @@
         <v>1</v>
       </c>
       <c r="K164" s="47" t="n">
-        <v>401.71</v>
+        <v>723.1799999999999</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -29694,12 +29838,12 @@
       </c>
       <c r="M164" s="49" t="inlineStr">
         <is>
-          <t>327158453</t>
+          <t>327127415</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1w16eZ2iuW4dPbkomePY18LR7CPlxsdYp/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1szeFukWcwJsTpYUKLKIKWZXLhy2sel8E/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29731,7 +29875,7 @@
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" s="47" t="n">
-        <v>580.51</v>
+        <v>401.71</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -29747,7 +29891,7 @@
         <v>1</v>
       </c>
       <c r="K165" s="47" t="n">
-        <v>580.51</v>
+        <v>401.71</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -29756,12 +29900,12 @@
       </c>
       <c r="M165" s="49" t="inlineStr">
         <is>
-          <t>327190672</t>
+          <t>327158453</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YGt6D24m8-UdGBL3aaHOe0wVC7k4qghi/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1w16eZ2iuW4dPbkomePY18LR7CPlxsdYp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29793,7 +29937,7 @@
       </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" s="47" t="n">
-        <v>7.91</v>
+        <v>580.51</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -29809,7 +29953,7 @@
         <v>1</v>
       </c>
       <c r="K166" s="47" t="n">
-        <v>7.91</v>
+        <v>580.51</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -29818,12 +29962,12 @@
       </c>
       <c r="M166" s="49" t="inlineStr">
         <is>
-          <t>838283238</t>
+          <t>327190672</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1enWtjyf2SUswvIm0_3r2ARUO4Nc_9Jd0/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YGt6D24m8-UdGBL3aaHOe0wVC7k4qghi/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29840,22 +29984,22 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" s="47" t="n">
-        <v>369</v>
+        <v>7.91</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -29871,7 +30015,7 @@
         <v>1</v>
       </c>
       <c r="K167" s="47" t="n">
-        <v>369</v>
+        <v>7.91</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -29880,12 +30024,12 @@
       </c>
       <c r="M167" s="49" t="inlineStr">
         <is>
-          <t>IFC2603-18831</t>
+          <t>838283238</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YylC1UsF8Mmxn_K1BFQWDm5IBpU5pT4S/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1enWtjyf2SUswvIm0_3r2ARUO4Nc_9Jd0/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -29907,17 +30051,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" s="47" t="n">
-        <v>440</v>
+        <v>369</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -29933,7 +30077,7 @@
         <v>1</v>
       </c>
       <c r="K168" s="47" t="n">
-        <v>440</v>
+        <v>369</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -29942,19 +30086,19 @@
       </c>
       <c r="M168" s="49" t="inlineStr">
         <is>
-          <t>OQXBYXMP-0006</t>
+          <t>IFC2603-18831</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Dfe3TUTMjwwXhP0sW7OA-brj3bzdreVa/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YylC1UsF8Mmxn_K1BFQWDm5IBpU5pT4S/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="169" ht="12" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -29969,17 +30113,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
       <c r="G169" s="47" t="n">
-        <v>808.08</v>
+        <v>440</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -29995,7 +30139,7 @@
         <v>1</v>
       </c>
       <c r="K169" s="47" t="n">
-        <v>808.08</v>
+        <v>440</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -30004,12 +30148,12 @@
       </c>
       <c r="M169" s="49" t="inlineStr">
         <is>
-          <t>F01033/26</t>
+          <t>OQXBYXMP-0006</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1YU4Rv32gQWRnZltbnXYoiABaHUadZkPC/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Dfe3TUTMjwwXhP0sW7OA-brj3bzdreVa/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -30031,21 +30175,21 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" s="47" t="n">
-        <v>32.14</v>
+        <v>808.08</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -30054,10 +30198,10 @@
         </is>
       </c>
       <c r="J170" s="48" t="n">
-        <v>0.85579803</v>
+        <v>1</v>
       </c>
       <c r="K170" s="47" t="n">
-        <v>27.51</v>
+        <v>808.08</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -30066,12 +30210,12 @@
       </c>
       <c r="M170" s="49" t="inlineStr">
         <is>
-          <t>1602C2F5-0018</t>
+          <t>F01033/26</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CAMDKbnRLAc0BtTnaayjMCU0RGZ6dmCJ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YU4Rv32gQWRnZltbnXYoiABaHUadZkPC/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -30098,16 +30242,16 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" s="47" t="n">
-        <v>135.59</v>
+        <v>32.14</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -30116,10 +30260,10 @@
         </is>
       </c>
       <c r="J171" s="48" t="n">
-        <v>1</v>
+        <v>0.85579803</v>
       </c>
       <c r="K171" s="47" t="n">
-        <v>135.59</v>
+        <v>27.51</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -30128,12 +30272,12 @@
       </c>
       <c r="M171" s="49" t="inlineStr">
         <is>
-          <t>RVR-19093</t>
+          <t>1602C2F5-0018</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1a9PDsbMBEl6jr1J063Bas9xJ16j0K-Vt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CAMDKbnRLAc0BtTnaayjMCU0RGZ6dmCJ/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -30155,17 +30299,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
       <c r="G172" s="47" t="n">
-        <v>15</v>
+        <v>135.59</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -30181,7 +30325,7 @@
         <v>1</v>
       </c>
       <c r="K172" s="47" t="n">
-        <v>15</v>
+        <v>135.59</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -30190,19 +30334,19 @@
       </c>
       <c r="M172" s="49" t="inlineStr">
         <is>
-          <t>7/1074</t>
+          <t>RVR-19093</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11QFEdz-ALQYNgRguLCU4q390nTPxudFV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1a9PDsbMBEl6jr1J063Bas9xJ16j0K-Vt/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="173" ht="12" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -30212,22 +30356,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" s="47" t="n">
-        <v>13737</v>
+        <v>15</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -30243,20 +30387,28 @@
         <v>1</v>
       </c>
       <c r="K173" s="47" t="n">
-        <v>13737</v>
+        <v>15</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M173" s="49" t="inlineStr">
+        <is>
+          <t>7/1074</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11QFEdz-ALQYNgRguLCU4q390nTPxudFV/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="12" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -30281,7 +30433,7 @@
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" s="47" t="n">
-        <v>16662</v>
+        <v>13737</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -30297,7 +30449,7 @@
         <v>1</v>
       </c>
       <c r="K174" s="47" t="n">
-        <v>16662</v>
+        <v>13737</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -30310,7 +30462,7 @@
     <row r="175" ht="12" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -30335,7 +30487,7 @@
       </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" s="47" t="n">
-        <v>14544</v>
+        <v>16662</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -30351,7 +30503,7 @@
         <v>1</v>
       </c>
       <c r="K175" s="47" t="n">
-        <v>14544</v>
+        <v>16662</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -30364,7 +30516,7 @@
     <row r="176" ht="12" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -30374,22 +30526,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>royalties</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>ROYALTIES</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" s="47" t="n">
-        <v>14731.84</v>
+        <v>14544</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -30405,11 +30557,11 @@
         <v>1</v>
       </c>
       <c r="K176" s="47" t="n">
-        <v>14731.84</v>
+        <v>14544</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
+          <t>artist_royalties_monthly_summary</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
@@ -30418,7 +30570,7 @@
     <row r="177" ht="12" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -30443,7 +30595,7 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" s="47" t="n">
-        <v>14915.68</v>
+        <v>14731.84</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -30459,7 +30611,7 @@
         <v>1</v>
       </c>
       <c r="K177" s="47" t="n">
-        <v>14915.68</v>
+        <v>14731.84</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -30472,7 +30624,7 @@
     <row r="178" ht="12" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -30497,7 +30649,7 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" s="47" t="n">
-        <v>15349.42</v>
+        <v>14915.68</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -30513,7 +30665,7 @@
         <v>1</v>
       </c>
       <c r="K178" s="47" t="n">
-        <v>15349.42</v>
+        <v>14915.68</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -30526,7 +30678,7 @@
     <row r="179" ht="12" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -30541,21 +30693,17 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Otros gastos enero 2026</t>
-        </is>
-      </c>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" s="47" t="n">
-        <v>411.87</v>
+        <v>15349.42</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -30571,11 +30719,11 @@
         <v>1</v>
       </c>
       <c r="K179" s="47" t="n">
-        <v>411.87</v>
+        <v>15349.42</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>payroll_documents</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
@@ -30584,7 +30732,7 @@
     <row r="180" ht="12" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -30609,11 +30757,11 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Otros gastos febrero 2026</t>
+          <t>Otros gastos enero 2026</t>
         </is>
       </c>
       <c r="G180" s="47" t="n">
-        <v>554.46</v>
+        <v>411.87</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -30629,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="K180" s="47" t="n">
-        <v>554.46</v>
+        <v>411.87</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -30638,6 +30786,64 @@
       </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
+    </row>
+    <row r="181" ht="12" customHeight="1">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Otros gastos febrero 2026</t>
+        </is>
+      </c>
+      <c r="G181" s="47" t="n">
+        <v>554.46</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J181" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" s="47" t="n">
+        <v>554.46</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -30706,7 +30912,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId68"/>
@@ -30810,6 +31016,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
